--- a/1.training_model/supplementary/df_trainingdatatset.xlsx
+++ b/1.training_model/supplementary/df_trainingdatatset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sitisyaziyah\source\repos\DeviceCluster\1.training_model\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B18EF53B-4184-4312-ACC3-65F1477C0F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A796A7D4-17FE-4D10-8FFF-838BBE6CCE3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1569</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -5275,393 +5288,393 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B7" t="s">
-        <v>498</v>
+        <v>717</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>505</v>
+        <v>938</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B8" t="s">
-        <v>498</v>
+        <v>717</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E8" t="s">
-        <v>513</v>
+        <v>941</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B9" t="s">
-        <v>607</v>
+        <v>717</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E9" t="s">
-        <v>614</v>
+        <v>944</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B10" t="s">
-        <v>607</v>
+        <v>1049</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E10" t="s">
-        <v>622</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B11" t="s">
-        <v>369</v>
+        <v>1127</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E11" t="s">
-        <v>376</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B12" t="s">
-        <v>369</v>
+        <v>1127</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>384</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B13" t="s">
-        <v>275</v>
+        <v>1127</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
-        <v>282</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B14" t="s">
-        <v>275</v>
+        <v>1243</v>
       </c>
       <c r="C14" t="s">
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E14" t="s">
-        <v>289</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B15" t="s">
-        <v>6</v>
+        <v>1243</v>
       </c>
       <c r="C15" t="s">
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>1243</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E16" t="s">
-        <v>24</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>1359</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
-        <v>153</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B18" t="s">
-        <v>146</v>
+        <v>1359</v>
       </c>
       <c r="C18" t="s">
         <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E18" t="s">
-        <v>161</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B19" t="s">
-        <v>498</v>
+        <v>1359</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>506</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B20" t="s">
-        <v>607</v>
+        <v>1475</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E20" t="s">
-        <v>615</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B21" t="s">
-        <v>369</v>
+        <v>1475</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>377</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B22" t="s">
-        <v>275</v>
+        <v>1475</v>
       </c>
       <c r="C22" t="s">
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E22" t="s">
-        <v>283</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B23" t="s">
-        <v>6</v>
+        <v>717</v>
       </c>
       <c r="C23" t="s">
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E23" t="s">
-        <v>17</v>
+        <v>913</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B24" t="s">
-        <v>146</v>
+        <v>717</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>8</v>
+        <v>794</v>
       </c>
       <c r="E24" t="s">
-        <v>154</v>
+        <v>958</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B25" t="s">
-        <v>498</v>
+        <v>717</v>
       </c>
       <c r="C25" t="s">
         <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>8</v>
+        <v>844</v>
       </c>
       <c r="E25" t="s">
-        <v>504</v>
+        <v>983</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B26" t="s">
-        <v>498</v>
+        <v>717</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>8</v>
+        <v>844</v>
       </c>
       <c r="E26" t="s">
-        <v>507</v>
+        <v>984</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B27" t="s">
-        <v>498</v>
+        <v>1127</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E27" t="s">
-        <v>516</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B28" t="s">
-        <v>607</v>
+        <v>1243</v>
       </c>
       <c r="C28" t="s">
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E28" t="s">
-        <v>613</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B29" t="s">
-        <v>607</v>
+        <v>1359</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E29" t="s">
-        <v>616</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
@@ -7451,19 +7464,19 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B135" t="s">
-        <v>607</v>
+        <v>1475</v>
       </c>
       <c r="C135" t="s">
         <v>14</v>
       </c>
       <c r="D135" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E135" t="s">
-        <v>625</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
@@ -7471,7 +7484,7 @@
         <v>5</v>
       </c>
       <c r="B136" t="s">
-        <v>369</v>
+        <v>498</v>
       </c>
       <c r="C136" t="s">
         <v>14</v>
@@ -7480,7 +7493,7 @@
         <v>8</v>
       </c>
       <c r="E136" t="s">
-        <v>375</v>
+        <v>505</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
@@ -7488,7 +7501,7 @@
         <v>5</v>
       </c>
       <c r="B137" t="s">
-        <v>369</v>
+        <v>498</v>
       </c>
       <c r="C137" t="s">
         <v>14</v>
@@ -7497,7 +7510,7 @@
         <v>8</v>
       </c>
       <c r="E137" t="s">
-        <v>378</v>
+        <v>513</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.35">
@@ -7505,7 +7518,7 @@
         <v>5</v>
       </c>
       <c r="B138" t="s">
-        <v>369</v>
+        <v>607</v>
       </c>
       <c r="C138" t="s">
         <v>14</v>
@@ -7514,7 +7527,7 @@
         <v>8</v>
       </c>
       <c r="E138" t="s">
-        <v>387</v>
+        <v>614</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.35">
@@ -7522,7 +7535,7 @@
         <v>5</v>
       </c>
       <c r="B139" t="s">
-        <v>275</v>
+        <v>607</v>
       </c>
       <c r="C139" t="s">
         <v>14</v>
@@ -7531,7 +7544,7 @@
         <v>8</v>
       </c>
       <c r="E139" t="s">
-        <v>281</v>
+        <v>622</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
@@ -7539,7 +7552,7 @@
         <v>5</v>
       </c>
       <c r="B140" t="s">
-        <v>6</v>
+        <v>369</v>
       </c>
       <c r="C140" t="s">
         <v>14</v>
@@ -7548,7 +7561,7 @@
         <v>8</v>
       </c>
       <c r="E140" t="s">
-        <v>15</v>
+        <v>376</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
@@ -7556,7 +7569,7 @@
         <v>5</v>
       </c>
       <c r="B141" t="s">
-        <v>6</v>
+        <v>369</v>
       </c>
       <c r="C141" t="s">
         <v>14</v>
@@ -7565,7 +7578,7 @@
         <v>8</v>
       </c>
       <c r="E141" t="s">
-        <v>18</v>
+        <v>384</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.35">
@@ -7573,7 +7586,7 @@
         <v>5</v>
       </c>
       <c r="B142" t="s">
-        <v>6</v>
+        <v>275</v>
       </c>
       <c r="C142" t="s">
         <v>14</v>
@@ -7582,7 +7595,7 @@
         <v>8</v>
       </c>
       <c r="E142" t="s">
-        <v>27</v>
+        <v>282</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.35">
@@ -7590,7 +7603,7 @@
         <v>5</v>
       </c>
       <c r="B143" t="s">
-        <v>146</v>
+        <v>275</v>
       </c>
       <c r="C143" t="s">
         <v>14</v>
@@ -7599,7 +7612,7 @@
         <v>8</v>
       </c>
       <c r="E143" t="s">
-        <v>152</v>
+        <v>289</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
@@ -7607,7 +7620,7 @@
         <v>5</v>
       </c>
       <c r="B144" t="s">
-        <v>146</v>
+        <v>6</v>
       </c>
       <c r="C144" t="s">
         <v>14</v>
@@ -7616,7 +7629,7 @@
         <v>8</v>
       </c>
       <c r="E144" t="s">
-        <v>155</v>
+        <v>16</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
@@ -7624,7 +7637,7 @@
         <v>5</v>
       </c>
       <c r="B145" t="s">
-        <v>146</v>
+        <v>6</v>
       </c>
       <c r="C145" t="s">
         <v>14</v>
@@ -7633,7 +7646,7 @@
         <v>8</v>
       </c>
       <c r="E145" t="s">
-        <v>164</v>
+        <v>24</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
@@ -7641,7 +7654,7 @@
         <v>5</v>
       </c>
       <c r="B146" t="s">
-        <v>498</v>
+        <v>146</v>
       </c>
       <c r="C146" t="s">
         <v>14</v>
@@ -7650,7 +7663,7 @@
         <v>8</v>
       </c>
       <c r="E146" t="s">
-        <v>514</v>
+        <v>153</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
@@ -7658,7 +7671,7 @@
         <v>5</v>
       </c>
       <c r="B147" t="s">
-        <v>607</v>
+        <v>146</v>
       </c>
       <c r="C147" t="s">
         <v>14</v>
@@ -7667,7 +7680,7 @@
         <v>8</v>
       </c>
       <c r="E147" t="s">
-        <v>623</v>
+        <v>161</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
@@ -7675,7 +7688,7 @@
         <v>5</v>
       </c>
       <c r="B148" t="s">
-        <v>369</v>
+        <v>498</v>
       </c>
       <c r="C148" t="s">
         <v>14</v>
@@ -7684,7 +7697,7 @@
         <v>8</v>
       </c>
       <c r="E148" t="s">
-        <v>385</v>
+        <v>506</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
@@ -7692,7 +7705,7 @@
         <v>5</v>
       </c>
       <c r="B149" t="s">
-        <v>275</v>
+        <v>607</v>
       </c>
       <c r="C149" t="s">
         <v>14</v>
@@ -7701,7 +7714,7 @@
         <v>8</v>
       </c>
       <c r="E149" t="s">
-        <v>290</v>
+        <v>615</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
@@ -7709,7 +7722,7 @@
         <v>5</v>
       </c>
       <c r="B150" t="s">
-        <v>6</v>
+        <v>369</v>
       </c>
       <c r="C150" t="s">
         <v>14</v>
@@ -7718,7 +7731,7 @@
         <v>8</v>
       </c>
       <c r="E150" t="s">
-        <v>25</v>
+        <v>377</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
@@ -7726,7 +7739,7 @@
         <v>5</v>
       </c>
       <c r="B151" t="s">
-        <v>146</v>
+        <v>275</v>
       </c>
       <c r="C151" t="s">
         <v>14</v>
@@ -7735,7 +7748,7 @@
         <v>8</v>
       </c>
       <c r="E151" t="s">
-        <v>162</v>
+        <v>283</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
@@ -7743,7 +7756,7 @@
         <v>5</v>
       </c>
       <c r="B152" t="s">
-        <v>498</v>
+        <v>6</v>
       </c>
       <c r="C152" t="s">
         <v>14</v>
@@ -7752,7 +7765,7 @@
         <v>8</v>
       </c>
       <c r="E152" t="s">
-        <v>508</v>
+        <v>17</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.35">
@@ -7760,7 +7773,7 @@
         <v>5</v>
       </c>
       <c r="B153" t="s">
-        <v>607</v>
+        <v>146</v>
       </c>
       <c r="C153" t="s">
         <v>14</v>
@@ -7769,7 +7782,7 @@
         <v>8</v>
       </c>
       <c r="E153" t="s">
-        <v>617</v>
+        <v>154</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
@@ -7777,7 +7790,7 @@
         <v>5</v>
       </c>
       <c r="B154" t="s">
-        <v>369</v>
+        <v>498</v>
       </c>
       <c r="C154" t="s">
         <v>14</v>
@@ -7786,7 +7799,7 @@
         <v>8</v>
       </c>
       <c r="E154" t="s">
-        <v>379</v>
+        <v>504</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
@@ -7794,7 +7807,7 @@
         <v>5</v>
       </c>
       <c r="B155" t="s">
-        <v>275</v>
+        <v>498</v>
       </c>
       <c r="C155" t="s">
         <v>14</v>
@@ -7803,7 +7816,7 @@
         <v>8</v>
       </c>
       <c r="E155" t="s">
-        <v>284</v>
+        <v>507</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
@@ -7811,7 +7824,7 @@
         <v>5</v>
       </c>
       <c r="B156" t="s">
-        <v>6</v>
+        <v>498</v>
       </c>
       <c r="C156" t="s">
         <v>14</v>
@@ -7820,7 +7833,7 @@
         <v>8</v>
       </c>
       <c r="E156" t="s">
-        <v>19</v>
+        <v>516</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.35">
@@ -7828,7 +7841,7 @@
         <v>5</v>
       </c>
       <c r="B157" t="s">
-        <v>146</v>
+        <v>607</v>
       </c>
       <c r="C157" t="s">
         <v>14</v>
@@ -7837,7 +7850,7 @@
         <v>8</v>
       </c>
       <c r="E157" t="s">
-        <v>156</v>
+        <v>613</v>
       </c>
     </row>
     <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
@@ -9630,7 +9643,7 @@
         <v>5</v>
       </c>
       <c r="B263" t="s">
-        <v>498</v>
+        <v>607</v>
       </c>
       <c r="C263" t="s">
         <v>14</v>
@@ -9639,7 +9652,7 @@
         <v>8</v>
       </c>
       <c r="E263" t="s">
-        <v>509</v>
+        <v>616</v>
       </c>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.35">
@@ -9647,7 +9660,7 @@
         <v>5</v>
       </c>
       <c r="B264" t="s">
-        <v>498</v>
+        <v>607</v>
       </c>
       <c r="C264" t="s">
         <v>14</v>
@@ -9656,7 +9669,7 @@
         <v>8</v>
       </c>
       <c r="E264" t="s">
-        <v>511</v>
+        <v>625</v>
       </c>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.35">
@@ -9664,7 +9677,7 @@
         <v>5</v>
       </c>
       <c r="B265" t="s">
-        <v>607</v>
+        <v>369</v>
       </c>
       <c r="C265" t="s">
         <v>14</v>
@@ -9673,7 +9686,7 @@
         <v>8</v>
       </c>
       <c r="E265" t="s">
-        <v>618</v>
+        <v>375</v>
       </c>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.35">
@@ -9681,7 +9694,7 @@
         <v>5</v>
       </c>
       <c r="B266" t="s">
-        <v>607</v>
+        <v>369</v>
       </c>
       <c r="C266" t="s">
         <v>14</v>
@@ -9690,7 +9703,7 @@
         <v>8</v>
       </c>
       <c r="E266" t="s">
-        <v>620</v>
+        <v>378</v>
       </c>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.35">
@@ -9707,7 +9720,7 @@
         <v>8</v>
       </c>
       <c r="E267" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.35">
@@ -9715,7 +9728,7 @@
         <v>5</v>
       </c>
       <c r="B268" t="s">
-        <v>369</v>
+        <v>275</v>
       </c>
       <c r="C268" t="s">
         <v>14</v>
@@ -9724,7 +9737,7 @@
         <v>8</v>
       </c>
       <c r="E268" t="s">
-        <v>382</v>
+        <v>281</v>
       </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.35">
@@ -9732,7 +9745,7 @@
         <v>5</v>
       </c>
       <c r="B269" t="s">
-        <v>275</v>
+        <v>6</v>
       </c>
       <c r="C269" t="s">
         <v>14</v>
@@ -9741,7 +9754,7 @@
         <v>8</v>
       </c>
       <c r="E269" t="s">
-        <v>285</v>
+        <v>15</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.35">
@@ -9749,7 +9762,7 @@
         <v>5</v>
       </c>
       <c r="B270" t="s">
-        <v>275</v>
+        <v>6</v>
       </c>
       <c r="C270" t="s">
         <v>14</v>
@@ -9758,7 +9771,7 @@
         <v>8</v>
       </c>
       <c r="E270" t="s">
-        <v>287</v>
+        <v>18</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.35">
@@ -9775,7 +9788,7 @@
         <v>8</v>
       </c>
       <c r="E271" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.35">
@@ -9783,7 +9796,7 @@
         <v>5</v>
       </c>
       <c r="B272" t="s">
-        <v>6</v>
+        <v>146</v>
       </c>
       <c r="C272" t="s">
         <v>14</v>
@@ -9792,7 +9805,7 @@
         <v>8</v>
       </c>
       <c r="E272" t="s">
-        <v>22</v>
+        <v>152</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.35">
@@ -9809,7 +9822,7 @@
         <v>8</v>
       </c>
       <c r="E273" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.35">
@@ -9826,143 +9839,143 @@
         <v>8</v>
       </c>
       <c r="E274" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B275" t="s">
-        <v>498</v>
+        <v>717</v>
       </c>
       <c r="C275" t="s">
         <v>14</v>
       </c>
       <c r="D275" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E275" t="s">
-        <v>510</v>
+        <v>939</v>
       </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B276" t="s">
-        <v>498</v>
+        <v>717</v>
       </c>
       <c r="C276" t="s">
         <v>14</v>
       </c>
       <c r="D276" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E276" t="s">
-        <v>512</v>
+        <v>940</v>
       </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B277" t="s">
-        <v>607</v>
+        <v>717</v>
       </c>
       <c r="C277" t="s">
         <v>14</v>
       </c>
       <c r="D277" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E277" t="s">
-        <v>619</v>
+        <v>947</v>
       </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B278" t="s">
-        <v>607</v>
+        <v>717</v>
       </c>
       <c r="C278" t="s">
         <v>14</v>
       </c>
       <c r="D278" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E278" t="s">
-        <v>621</v>
+        <v>948</v>
       </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B279" t="s">
-        <v>369</v>
+        <v>717</v>
       </c>
       <c r="C279" t="s">
         <v>14</v>
       </c>
       <c r="D279" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E279" t="s">
-        <v>381</v>
+        <v>949</v>
       </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B280" t="s">
-        <v>369</v>
+        <v>1049</v>
       </c>
       <c r="C280" t="s">
         <v>14</v>
       </c>
       <c r="D280" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E280" t="s">
-        <v>383</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B281" t="s">
-        <v>275</v>
+        <v>1049</v>
       </c>
       <c r="C281" t="s">
         <v>14</v>
       </c>
       <c r="D281" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E281" t="s">
-        <v>286</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B282" t="s">
-        <v>275</v>
+        <v>1127</v>
       </c>
       <c r="C282" t="s">
         <v>14</v>
       </c>
       <c r="D282" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E282" t="s">
-        <v>288</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
@@ -11208,121 +11221,121 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B356" t="s">
-        <v>6</v>
+        <v>1127</v>
       </c>
       <c r="C356" t="s">
         <v>14</v>
       </c>
       <c r="D356" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E356" t="s">
-        <v>21</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B357" t="s">
-        <v>6</v>
+        <v>1243</v>
       </c>
       <c r="C357" t="s">
         <v>14</v>
       </c>
       <c r="D357" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E357" t="s">
-        <v>23</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B358" t="s">
-        <v>146</v>
+        <v>1243</v>
       </c>
       <c r="C358" t="s">
         <v>14</v>
       </c>
       <c r="D358" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E358" t="s">
-        <v>158</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B359" t="s">
-        <v>146</v>
+        <v>1359</v>
       </c>
       <c r="C359" t="s">
         <v>14</v>
       </c>
       <c r="D359" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E359" t="s">
-        <v>160</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B360" t="s">
-        <v>498</v>
+        <v>1359</v>
       </c>
       <c r="C360" t="s">
         <v>14</v>
       </c>
       <c r="D360" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E360" t="s">
-        <v>515</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B361" t="s">
-        <v>607</v>
+        <v>1475</v>
       </c>
       <c r="C361" t="s">
         <v>14</v>
       </c>
       <c r="D361" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E361" t="s">
-        <v>624</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B362" t="s">
-        <v>369</v>
+        <v>1475</v>
       </c>
       <c r="C362" t="s">
         <v>14</v>
       </c>
       <c r="D362" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E362" t="s">
-        <v>386</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.35">
@@ -11330,7 +11343,7 @@
         <v>5</v>
       </c>
       <c r="B363" t="s">
-        <v>275</v>
+        <v>498</v>
       </c>
       <c r="C363" t="s">
         <v>14</v>
@@ -11339,7 +11352,7 @@
         <v>8</v>
       </c>
       <c r="E363" t="s">
-        <v>291</v>
+        <v>514</v>
       </c>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.35">
@@ -11347,7 +11360,7 @@
         <v>5</v>
       </c>
       <c r="B364" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="C364" t="s">
         <v>14</v>
@@ -11356,7 +11369,7 @@
         <v>8</v>
       </c>
       <c r="E364" t="s">
-        <v>26</v>
+        <v>623</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.35">
@@ -11364,7 +11377,7 @@
         <v>5</v>
       </c>
       <c r="B365" t="s">
-        <v>146</v>
+        <v>369</v>
       </c>
       <c r="C365" t="s">
         <v>14</v>
@@ -11373,7 +11386,7 @@
         <v>8</v>
       </c>
       <c r="E365" t="s">
-        <v>163</v>
+        <v>385</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.35">
@@ -11381,7 +11394,7 @@
         <v>5</v>
       </c>
       <c r="B366" t="s">
-        <v>498</v>
+        <v>275</v>
       </c>
       <c r="C366" t="s">
         <v>14</v>
@@ -11390,7 +11403,7 @@
         <v>8</v>
       </c>
       <c r="E366" t="s">
-        <v>517</v>
+        <v>290</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.35">
@@ -11398,7 +11411,7 @@
         <v>5</v>
       </c>
       <c r="B367" t="s">
-        <v>498</v>
+        <v>6</v>
       </c>
       <c r="C367" t="s">
         <v>14</v>
@@ -11407,7 +11420,7 @@
         <v>8</v>
       </c>
       <c r="E367" t="s">
-        <v>518</v>
+        <v>25</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.35">
@@ -11415,7 +11428,7 @@
         <v>5</v>
       </c>
       <c r="B368" t="s">
-        <v>607</v>
+        <v>146</v>
       </c>
       <c r="C368" t="s">
         <v>14</v>
@@ -11424,177 +11437,177 @@
         <v>8</v>
       </c>
       <c r="E368" t="s">
-        <v>626</v>
+        <v>162</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B369" t="s">
-        <v>607</v>
+        <v>717</v>
       </c>
       <c r="C369" t="s">
         <v>14</v>
       </c>
       <c r="D369" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E369" t="s">
-        <v>627</v>
+        <v>942</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B370" t="s">
-        <v>369</v>
+        <v>717</v>
       </c>
       <c r="C370" t="s">
         <v>14</v>
       </c>
       <c r="D370" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E370" t="s">
-        <v>388</v>
+        <v>945</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B371" t="s">
-        <v>369</v>
+        <v>1049</v>
       </c>
       <c r="C371" t="s">
         <v>14</v>
       </c>
       <c r="D371" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E371" t="s">
-        <v>389</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B372" t="s">
-        <v>275</v>
+        <v>1127</v>
       </c>
       <c r="C372" t="s">
         <v>14</v>
       </c>
       <c r="D372" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E372" t="s">
-        <v>292</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B373" t="s">
-        <v>275</v>
+        <v>1127</v>
       </c>
       <c r="C373" t="s">
         <v>14</v>
       </c>
       <c r="D373" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E373" t="s">
-        <v>293</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B374" t="s">
-        <v>6</v>
+        <v>1243</v>
       </c>
       <c r="C374" t="s">
         <v>14</v>
       </c>
       <c r="D374" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E374" t="s">
-        <v>28</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B375" t="s">
-        <v>6</v>
+        <v>1243</v>
       </c>
       <c r="C375" t="s">
         <v>14</v>
       </c>
       <c r="D375" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E375" t="s">
-        <v>29</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B376" t="s">
-        <v>146</v>
+        <v>1359</v>
       </c>
       <c r="C376" t="s">
         <v>14</v>
       </c>
       <c r="D376" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E376" t="s">
-        <v>165</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B377" t="s">
-        <v>146</v>
+        <v>1359</v>
       </c>
       <c r="C377" t="s">
         <v>14</v>
       </c>
       <c r="D377" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E377" t="s">
-        <v>166</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B378" t="s">
-        <v>498</v>
+        <v>1475</v>
       </c>
       <c r="C378" t="s">
         <v>14</v>
       </c>
       <c r="D378" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E378" t="s">
-        <v>519</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
@@ -13384,19 +13397,19 @@
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>5</v>
+        <v>716</v>
       </c>
       <c r="B484" t="s">
-        <v>607</v>
+        <v>1475</v>
       </c>
       <c r="C484" t="s">
         <v>14</v>
       </c>
       <c r="D484" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="E484" t="s">
-        <v>628</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.35">
@@ -13404,7 +13417,7 @@
         <v>5</v>
       </c>
       <c r="B485" t="s">
-        <v>369</v>
+        <v>498</v>
       </c>
       <c r="C485" t="s">
         <v>14</v>
@@ -13413,7 +13426,7 @@
         <v>8</v>
       </c>
       <c r="E485" t="s">
-        <v>390</v>
+        <v>508</v>
       </c>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.35">
@@ -13421,7 +13434,7 @@
         <v>5</v>
       </c>
       <c r="B486" t="s">
-        <v>275</v>
+        <v>607</v>
       </c>
       <c r="C486" t="s">
         <v>14</v>
@@ -13430,7 +13443,7 @@
         <v>8</v>
       </c>
       <c r="E486" t="s">
-        <v>294</v>
+        <v>617</v>
       </c>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.35">
@@ -13438,7 +13451,7 @@
         <v>5</v>
       </c>
       <c r="B487" t="s">
-        <v>6</v>
+        <v>369</v>
       </c>
       <c r="C487" t="s">
         <v>14</v>
@@ -13447,7 +13460,7 @@
         <v>8</v>
       </c>
       <c r="E487" t="s">
-        <v>30</v>
+        <v>379</v>
       </c>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.35">
@@ -13455,7 +13468,7 @@
         <v>5</v>
       </c>
       <c r="B488" t="s">
-        <v>146</v>
+        <v>275</v>
       </c>
       <c r="C488" t="s">
         <v>14</v>
@@ -13464,7 +13477,7 @@
         <v>8</v>
       </c>
       <c r="E488" t="s">
-        <v>167</v>
+        <v>284</v>
       </c>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.35">
@@ -13472,7 +13485,7 @@
         <v>5</v>
       </c>
       <c r="B489" t="s">
-        <v>498</v>
+        <v>6</v>
       </c>
       <c r="C489" t="s">
         <v>14</v>
@@ -13481,7 +13494,7 @@
         <v>8</v>
       </c>
       <c r="E489" t="s">
-        <v>520</v>
+        <v>19</v>
       </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.35">
@@ -13489,7 +13502,7 @@
         <v>5</v>
       </c>
       <c r="B490" t="s">
-        <v>498</v>
+        <v>146</v>
       </c>
       <c r="C490" t="s">
         <v>14</v>
@@ -13498,7 +13511,7 @@
         <v>8</v>
       </c>
       <c r="E490" t="s">
-        <v>521</v>
+        <v>156</v>
       </c>
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.35">
@@ -13515,7 +13528,7 @@
         <v>8</v>
       </c>
       <c r="E491" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.35">
@@ -13523,7 +13536,7 @@
         <v>5</v>
       </c>
       <c r="B492" t="s">
-        <v>607</v>
+        <v>498</v>
       </c>
       <c r="C492" t="s">
         <v>14</v>
@@ -13532,7 +13545,7 @@
         <v>8</v>
       </c>
       <c r="E492" t="s">
-        <v>629</v>
+        <v>511</v>
       </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.35">
@@ -13549,7 +13562,7 @@
         <v>8</v>
       </c>
       <c r="E493" t="s">
-        <v>630</v>
+        <v>618</v>
       </c>
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.35">
@@ -13566,7 +13579,7 @@
         <v>8</v>
       </c>
       <c r="E494" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.35">
@@ -13583,7 +13596,7 @@
         <v>8</v>
       </c>
       <c r="E495" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.35">
@@ -13600,7 +13613,7 @@
         <v>8</v>
       </c>
       <c r="E496" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.35">
@@ -13608,7 +13621,7 @@
         <v>5</v>
       </c>
       <c r="B497" t="s">
-        <v>369</v>
+        <v>275</v>
       </c>
       <c r="C497" t="s">
         <v>14</v>
@@ -13617,7 +13630,7 @@
         <v>8</v>
       </c>
       <c r="E497" t="s">
-        <v>393</v>
+        <v>285</v>
       </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.35">
@@ -13634,7 +13647,7 @@
         <v>8</v>
       </c>
       <c r="E498" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.35">
@@ -13642,7 +13655,7 @@
         <v>5</v>
       </c>
       <c r="B499" t="s">
-        <v>275</v>
+        <v>6</v>
       </c>
       <c r="C499" t="s">
         <v>14</v>
@@ -13651,7 +13664,7 @@
         <v>8</v>
       </c>
       <c r="E499" t="s">
-        <v>296</v>
+        <v>20</v>
       </c>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.35">
@@ -13659,7 +13672,7 @@
         <v>5</v>
       </c>
       <c r="B500" t="s">
-        <v>275</v>
+        <v>6</v>
       </c>
       <c r="C500" t="s">
         <v>14</v>
@@ -13668,7 +13681,7 @@
         <v>8</v>
       </c>
       <c r="E500" t="s">
-        <v>297</v>
+        <v>22</v>
       </c>
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.35">
@@ -13676,7 +13689,7 @@
         <v>5</v>
       </c>
       <c r="B501" t="s">
-        <v>6</v>
+        <v>146</v>
       </c>
       <c r="C501" t="s">
         <v>14</v>
@@ -13685,7 +13698,7 @@
         <v>8</v>
       </c>
       <c r="E501" t="s">
-        <v>31</v>
+        <v>157</v>
       </c>
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.35">
@@ -13693,7 +13706,7 @@
         <v>5</v>
       </c>
       <c r="B502" t="s">
-        <v>6</v>
+        <v>146</v>
       </c>
       <c r="C502" t="s">
         <v>14</v>
@@ -13702,7 +13715,7 @@
         <v>8</v>
       </c>
       <c r="E502" t="s">
-        <v>32</v>
+        <v>159</v>
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.35">
@@ -13710,7 +13723,7 @@
         <v>5</v>
       </c>
       <c r="B503" t="s">
-        <v>6</v>
+        <v>498</v>
       </c>
       <c r="C503" t="s">
         <v>14</v>
@@ -13719,7 +13732,7 @@
         <v>8</v>
       </c>
       <c r="E503" t="s">
-        <v>33</v>
+        <v>510</v>
       </c>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.35">
@@ -13727,7 +13740,7 @@
         <v>5</v>
       </c>
       <c r="B504" t="s">
-        <v>146</v>
+        <v>498</v>
       </c>
       <c r="C504" t="s">
         <v>14</v>
@@ -13736,7 +13749,7 @@
         <v>8</v>
       </c>
       <c r="E504" t="s">
-        <v>168</v>
+        <v>512</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.35">
@@ -13744,7 +13757,7 @@
         <v>5</v>
       </c>
       <c r="B505" t="s">
-        <v>146</v>
+        <v>607</v>
       </c>
       <c r="C505" t="s">
         <v>14</v>
@@ -13753,7 +13766,7 @@
         <v>8</v>
       </c>
       <c r="E505" t="s">
-        <v>169</v>
+        <v>619</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.35">
@@ -13761,7 +13774,7 @@
         <v>5</v>
       </c>
       <c r="B506" t="s">
-        <v>146</v>
+        <v>607</v>
       </c>
       <c r="C506" t="s">
         <v>14</v>
@@ -13770,7 +13783,7 @@
         <v>8</v>
       </c>
       <c r="E506" t="s">
-        <v>170</v>
+        <v>621</v>
       </c>
     </row>
     <row r="507" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
@@ -15223,7 +15236,7 @@
         <v>5</v>
       </c>
       <c r="B592" t="s">
-        <v>498</v>
+        <v>369</v>
       </c>
       <c r="C592" t="s">
         <v>14</v>
@@ -15232,7 +15245,7 @@
         <v>8</v>
       </c>
       <c r="E592" t="s">
-        <v>523</v>
+        <v>381</v>
       </c>
     </row>
     <row r="593" spans="1:5" x14ac:dyDescent="0.35">
@@ -15240,7 +15253,7 @@
         <v>5</v>
       </c>
       <c r="B593" t="s">
-        <v>607</v>
+        <v>369</v>
       </c>
       <c r="C593" t="s">
         <v>14</v>
@@ -15249,7 +15262,7 @@
         <v>8</v>
       </c>
       <c r="E593" t="s">
-        <v>632</v>
+        <v>383</v>
       </c>
     </row>
     <row r="594" spans="1:5" x14ac:dyDescent="0.35">
@@ -15257,7 +15270,7 @@
         <v>5</v>
       </c>
       <c r="B594" t="s">
-        <v>369</v>
+        <v>275</v>
       </c>
       <c r="C594" t="s">
         <v>14</v>
@@ -15266,7 +15279,7 @@
         <v>8</v>
       </c>
       <c r="E594" t="s">
-        <v>394</v>
+        <v>286</v>
       </c>
     </row>
     <row r="595" spans="1:5" x14ac:dyDescent="0.35">
@@ -15274,7 +15287,7 @@
         <v>5</v>
       </c>
       <c r="B595" t="s">
-        <v>6</v>
+        <v>275</v>
       </c>
       <c r="C595" t="s">
         <v>14</v>
@@ -15283,7 +15296,7 @@
         <v>8</v>
       </c>
       <c r="E595" t="s">
-        <v>34</v>
+        <v>288</v>
       </c>
     </row>
     <row r="596" spans="1:5" x14ac:dyDescent="0.35">
@@ -15291,7 +15304,7 @@
         <v>5</v>
       </c>
       <c r="B596" t="s">
-        <v>146</v>
+        <v>6</v>
       </c>
       <c r="C596" t="s">
         <v>14</v>
@@ -15300,15 +15313,15 @@
         <v>8</v>
       </c>
       <c r="E596" t="s">
-        <v>171</v>
+        <v>21</v>
       </c>
     </row>
     <row r="597" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B597" t="s">
-        <v>717</v>
+        <v>6</v>
       </c>
       <c r="C597" t="s">
         <v>14</v>
@@ -15317,15 +15330,15 @@
         <v>8</v>
       </c>
       <c r="E597" t="s">
-        <v>893</v>
+        <v>23</v>
       </c>
     </row>
     <row r="598" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B598" t="s">
-        <v>717</v>
+        <v>146</v>
       </c>
       <c r="C598" t="s">
         <v>14</v>
@@ -15334,15 +15347,15 @@
         <v>8</v>
       </c>
       <c r="E598" t="s">
-        <v>894</v>
+        <v>158</v>
       </c>
     </row>
     <row r="599" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B599" t="s">
-        <v>717</v>
+        <v>146</v>
       </c>
       <c r="C599" t="s">
         <v>14</v>
@@ -15351,15 +15364,15 @@
         <v>8</v>
       </c>
       <c r="E599" t="s">
-        <v>895</v>
+        <v>160</v>
       </c>
     </row>
     <row r="600" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B600" t="s">
-        <v>717</v>
+        <v>498</v>
       </c>
       <c r="C600" t="s">
         <v>14</v>
@@ -15368,15 +15381,15 @@
         <v>8</v>
       </c>
       <c r="E600" t="s">
-        <v>896</v>
+        <v>515</v>
       </c>
     </row>
     <row r="601" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B601" t="s">
-        <v>717</v>
+        <v>607</v>
       </c>
       <c r="C601" t="s">
         <v>14</v>
@@ -15385,15 +15398,15 @@
         <v>8</v>
       </c>
       <c r="E601" t="s">
-        <v>897</v>
+        <v>624</v>
       </c>
     </row>
     <row r="602" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B602" t="s">
-        <v>717</v>
+        <v>369</v>
       </c>
       <c r="C602" t="s">
         <v>14</v>
@@ -15402,15 +15415,15 @@
         <v>8</v>
       </c>
       <c r="E602" t="s">
-        <v>898</v>
+        <v>386</v>
       </c>
     </row>
     <row r="603" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B603" t="s">
-        <v>717</v>
+        <v>275</v>
       </c>
       <c r="C603" t="s">
         <v>14</v>
@@ -15419,15 +15432,15 @@
         <v>8</v>
       </c>
       <c r="E603" t="s">
-        <v>899</v>
+        <v>291</v>
       </c>
     </row>
     <row r="604" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B604" t="s">
-        <v>717</v>
+        <v>6</v>
       </c>
       <c r="C604" t="s">
         <v>14</v>
@@ -15436,15 +15449,15 @@
         <v>8</v>
       </c>
       <c r="E604" t="s">
-        <v>900</v>
+        <v>26</v>
       </c>
     </row>
     <row r="605" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B605" t="s">
-        <v>1049</v>
+        <v>146</v>
       </c>
       <c r="C605" t="s">
         <v>14</v>
@@ -15453,15 +15466,15 @@
         <v>8</v>
       </c>
       <c r="E605" t="s">
-        <v>1086</v>
+        <v>163</v>
       </c>
     </row>
     <row r="606" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B606" t="s">
-        <v>1049</v>
+        <v>498</v>
       </c>
       <c r="C606" t="s">
         <v>14</v>
@@ -15470,15 +15483,15 @@
         <v>8</v>
       </c>
       <c r="E606" t="s">
-        <v>1087</v>
+        <v>517</v>
       </c>
     </row>
     <row r="607" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B607" t="s">
-        <v>1049</v>
+        <v>498</v>
       </c>
       <c r="C607" t="s">
         <v>14</v>
@@ -15487,15 +15500,15 @@
         <v>8</v>
       </c>
       <c r="E607" t="s">
-        <v>1088</v>
+        <v>518</v>
       </c>
     </row>
     <row r="608" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B608" t="s">
-        <v>1049</v>
+        <v>607</v>
       </c>
       <c r="C608" t="s">
         <v>14</v>
@@ -15504,15 +15517,15 @@
         <v>8</v>
       </c>
       <c r="E608" t="s">
-        <v>1089</v>
+        <v>626</v>
       </c>
     </row>
     <row r="609" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B609" t="s">
-        <v>1127</v>
+        <v>607</v>
       </c>
       <c r="C609" t="s">
         <v>14</v>
@@ -15521,15 +15534,15 @@
         <v>8</v>
       </c>
       <c r="E609" t="s">
-        <v>1185</v>
+        <v>627</v>
       </c>
     </row>
     <row r="610" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B610" t="s">
-        <v>1127</v>
+        <v>369</v>
       </c>
       <c r="C610" t="s">
         <v>14</v>
@@ -15538,15 +15551,15 @@
         <v>8</v>
       </c>
       <c r="E610" t="s">
-        <v>1186</v>
+        <v>388</v>
       </c>
     </row>
     <row r="611" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B611" t="s">
-        <v>1127</v>
+        <v>369</v>
       </c>
       <c r="C611" t="s">
         <v>14</v>
@@ -15555,15 +15568,15 @@
         <v>8</v>
       </c>
       <c r="E611" t="s">
-        <v>1187</v>
+        <v>389</v>
       </c>
     </row>
     <row r="612" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B612" t="s">
-        <v>1127</v>
+        <v>275</v>
       </c>
       <c r="C612" t="s">
         <v>14</v>
@@ -15572,15 +15585,15 @@
         <v>8</v>
       </c>
       <c r="E612" t="s">
-        <v>1188</v>
+        <v>292</v>
       </c>
     </row>
     <row r="613" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B613" t="s">
-        <v>1127</v>
+        <v>275</v>
       </c>
       <c r="C613" t="s">
         <v>14</v>
@@ -15589,7 +15602,7 @@
         <v>8</v>
       </c>
       <c r="E613" t="s">
-        <v>1189</v>
+        <v>293</v>
       </c>
     </row>
     <row r="614" spans="1:5" x14ac:dyDescent="0.35">
@@ -15597,7 +15610,7 @@
         <v>5</v>
       </c>
       <c r="B614" t="s">
-        <v>498</v>
+        <v>6</v>
       </c>
       <c r="C614" t="s">
         <v>14</v>
@@ -15606,7 +15619,7 @@
         <v>8</v>
       </c>
       <c r="E614" t="s">
-        <v>526</v>
+        <v>28</v>
       </c>
     </row>
     <row r="615" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
@@ -19881,7 +19894,7 @@
         <v>5</v>
       </c>
       <c r="B866" t="s">
-        <v>607</v>
+        <v>6</v>
       </c>
       <c r="C866" t="s">
         <v>14</v>
@@ -19890,15 +19903,15 @@
         <v>8</v>
       </c>
       <c r="E866" t="s">
-        <v>635</v>
+        <v>29</v>
       </c>
     </row>
     <row r="867" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A867" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B867" t="s">
-        <v>1243</v>
+        <v>146</v>
       </c>
       <c r="C867" t="s">
         <v>14</v>
@@ -19907,15 +19920,15 @@
         <v>8</v>
       </c>
       <c r="E867" t="s">
-        <v>1301</v>
+        <v>165</v>
       </c>
     </row>
     <row r="868" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A868" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B868" t="s">
-        <v>1243</v>
+        <v>146</v>
       </c>
       <c r="C868" t="s">
         <v>14</v>
@@ -19924,15 +19937,15 @@
         <v>8</v>
       </c>
       <c r="E868" t="s">
-        <v>1302</v>
+        <v>166</v>
       </c>
     </row>
     <row r="869" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A869" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B869" t="s">
-        <v>1243</v>
+        <v>498</v>
       </c>
       <c r="C869" t="s">
         <v>14</v>
@@ -19941,15 +19954,15 @@
         <v>8</v>
       </c>
       <c r="E869" t="s">
-        <v>1303</v>
+        <v>519</v>
       </c>
     </row>
     <row r="870" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A870" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B870" t="s">
-        <v>1243</v>
+        <v>607</v>
       </c>
       <c r="C870" t="s">
         <v>14</v>
@@ -19958,15 +19971,15 @@
         <v>8</v>
       </c>
       <c r="E870" t="s">
-        <v>1304</v>
+        <v>628</v>
       </c>
     </row>
     <row r="871" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A871" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B871" t="s">
-        <v>1243</v>
+        <v>369</v>
       </c>
       <c r="C871" t="s">
         <v>14</v>
@@ -19975,7 +19988,7 @@
         <v>8</v>
       </c>
       <c r="E871" t="s">
-        <v>1305</v>
+        <v>390</v>
       </c>
     </row>
     <row r="872" spans="1:5" x14ac:dyDescent="0.35">
@@ -19983,7 +19996,7 @@
         <v>5</v>
       </c>
       <c r="B872" t="s">
-        <v>369</v>
+        <v>275</v>
       </c>
       <c r="C872" t="s">
         <v>14</v>
@@ -19992,15 +20005,15 @@
         <v>8</v>
       </c>
       <c r="E872" t="s">
-        <v>397</v>
+        <v>294</v>
       </c>
     </row>
     <row r="873" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A873" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B873" t="s">
-        <v>1359</v>
+        <v>6</v>
       </c>
       <c r="C873" t="s">
         <v>14</v>
@@ -20009,15 +20022,15 @@
         <v>8</v>
       </c>
       <c r="E873" t="s">
-        <v>1417</v>
+        <v>30</v>
       </c>
     </row>
     <row r="874" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A874" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B874" t="s">
-        <v>1359</v>
+        <v>146</v>
       </c>
       <c r="C874" t="s">
         <v>14</v>
@@ -20026,15 +20039,15 @@
         <v>8</v>
       </c>
       <c r="E874" t="s">
-        <v>1418</v>
+        <v>167</v>
       </c>
     </row>
     <row r="875" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A875" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B875" t="s">
-        <v>1359</v>
+        <v>498</v>
       </c>
       <c r="C875" t="s">
         <v>14</v>
@@ -20043,15 +20056,15 @@
         <v>8</v>
       </c>
       <c r="E875" t="s">
-        <v>1419</v>
+        <v>520</v>
       </c>
     </row>
     <row r="876" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A876" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B876" t="s">
-        <v>1359</v>
+        <v>498</v>
       </c>
       <c r="C876" t="s">
         <v>14</v>
@@ -20060,15 +20073,15 @@
         <v>8</v>
       </c>
       <c r="E876" t="s">
-        <v>1420</v>
+        <v>521</v>
       </c>
     </row>
     <row r="877" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A877" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B877" t="s">
-        <v>1359</v>
+        <v>498</v>
       </c>
       <c r="C877" t="s">
         <v>14</v>
@@ -20077,7 +20090,7 @@
         <v>8</v>
       </c>
       <c r="E877" t="s">
-        <v>1421</v>
+        <v>522</v>
       </c>
     </row>
     <row r="878" spans="1:5" x14ac:dyDescent="0.35">
@@ -20085,7 +20098,7 @@
         <v>5</v>
       </c>
       <c r="B878" t="s">
-        <v>275</v>
+        <v>607</v>
       </c>
       <c r="C878" t="s">
         <v>14</v>
@@ -20094,7 +20107,7 @@
         <v>8</v>
       </c>
       <c r="E878" t="s">
-        <v>300</v>
+        <v>629</v>
       </c>
     </row>
     <row r="879" spans="1:5" x14ac:dyDescent="0.35">
@@ -20102,7 +20115,7 @@
         <v>5</v>
       </c>
       <c r="B879" t="s">
-        <v>6</v>
+        <v>607</v>
       </c>
       <c r="C879" t="s">
         <v>14</v>
@@ -20111,15 +20124,15 @@
         <v>8</v>
       </c>
       <c r="E879" t="s">
-        <v>37</v>
+        <v>630</v>
       </c>
     </row>
     <row r="880" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A880" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B880" t="s">
-        <v>1475</v>
+        <v>607</v>
       </c>
       <c r="C880" t="s">
         <v>14</v>
@@ -20128,15 +20141,15 @@
         <v>8</v>
       </c>
       <c r="E880" t="s">
-        <v>1534</v>
+        <v>631</v>
       </c>
     </row>
     <row r="881" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A881" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B881" t="s">
-        <v>1475</v>
+        <v>369</v>
       </c>
       <c r="C881" t="s">
         <v>14</v>
@@ -20145,15 +20158,15 @@
         <v>8</v>
       </c>
       <c r="E881" t="s">
-        <v>1535</v>
+        <v>391</v>
       </c>
     </row>
     <row r="882" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A882" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B882" t="s">
-        <v>1475</v>
+        <v>369</v>
       </c>
       <c r="C882" t="s">
         <v>14</v>
@@ -20162,15 +20175,15 @@
         <v>8</v>
       </c>
       <c r="E882" t="s">
-        <v>1536</v>
+        <v>392</v>
       </c>
     </row>
     <row r="883" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A883" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B883" t="s">
-        <v>1475</v>
+        <v>369</v>
       </c>
       <c r="C883" t="s">
         <v>14</v>
@@ -20179,15 +20192,15 @@
         <v>8</v>
       </c>
       <c r="E883" t="s">
-        <v>1537</v>
+        <v>393</v>
       </c>
     </row>
     <row r="884" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A884" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B884" t="s">
-        <v>1475</v>
+        <v>275</v>
       </c>
       <c r="C884" t="s">
         <v>14</v>
@@ -20196,7 +20209,7 @@
         <v>8</v>
       </c>
       <c r="E884" t="s">
-        <v>1538</v>
+        <v>295</v>
       </c>
     </row>
     <row r="885" spans="1:5" x14ac:dyDescent="0.35">
@@ -20204,7 +20217,7 @@
         <v>5</v>
       </c>
       <c r="B885" t="s">
-        <v>146</v>
+        <v>275</v>
       </c>
       <c r="C885" t="s">
         <v>14</v>
@@ -20213,7 +20226,7 @@
         <v>8</v>
       </c>
       <c r="E885" t="s">
-        <v>174</v>
+        <v>296</v>
       </c>
     </row>
     <row r="886" spans="1:5" x14ac:dyDescent="0.35">
@@ -20221,7 +20234,7 @@
         <v>5</v>
       </c>
       <c r="B886" t="s">
-        <v>498</v>
+        <v>275</v>
       </c>
       <c r="C886" t="s">
         <v>14</v>
@@ -20230,7 +20243,7 @@
         <v>8</v>
       </c>
       <c r="E886" t="s">
-        <v>524</v>
+        <v>297</v>
       </c>
     </row>
     <row r="887" spans="1:5" x14ac:dyDescent="0.35">
@@ -20238,7 +20251,7 @@
         <v>5</v>
       </c>
       <c r="B887" t="s">
-        <v>607</v>
+        <v>6</v>
       </c>
       <c r="C887" t="s">
         <v>14</v>
@@ -20247,7 +20260,7 @@
         <v>8</v>
       </c>
       <c r="E887" t="s">
-        <v>633</v>
+        <v>31</v>
       </c>
     </row>
     <row r="888" spans="1:5" x14ac:dyDescent="0.35">
@@ -20255,7 +20268,7 @@
         <v>5</v>
       </c>
       <c r="B888" t="s">
-        <v>369</v>
+        <v>6</v>
       </c>
       <c r="C888" t="s">
         <v>14</v>
@@ -20264,7 +20277,7 @@
         <v>8</v>
       </c>
       <c r="E888" t="s">
-        <v>395</v>
+        <v>32</v>
       </c>
     </row>
     <row r="889" spans="1:5" x14ac:dyDescent="0.35">
@@ -20272,7 +20285,7 @@
         <v>5</v>
       </c>
       <c r="B889" t="s">
-        <v>275</v>
+        <v>6</v>
       </c>
       <c r="C889" t="s">
         <v>14</v>
@@ -20281,7 +20294,7 @@
         <v>8</v>
       </c>
       <c r="E889" t="s">
-        <v>298</v>
+        <v>33</v>
       </c>
     </row>
     <row r="890" spans="1:5" x14ac:dyDescent="0.35">
@@ -20289,7 +20302,7 @@
         <v>5</v>
       </c>
       <c r="B890" t="s">
-        <v>6</v>
+        <v>146</v>
       </c>
       <c r="C890" t="s">
         <v>14</v>
@@ -20298,7 +20311,7 @@
         <v>8</v>
       </c>
       <c r="E890" t="s">
-        <v>35</v>
+        <v>168</v>
       </c>
     </row>
     <row r="891" spans="1:5" x14ac:dyDescent="0.35">
@@ -20315,7 +20328,7 @@
         <v>8</v>
       </c>
       <c r="E891" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="892" spans="1:5" x14ac:dyDescent="0.35">
@@ -20323,7 +20336,7 @@
         <v>5</v>
       </c>
       <c r="B892" t="s">
-        <v>498</v>
+        <v>146</v>
       </c>
       <c r="C892" t="s">
         <v>14</v>
@@ -20332,7 +20345,7 @@
         <v>8</v>
       </c>
       <c r="E892" t="s">
-        <v>525</v>
+        <v>170</v>
       </c>
     </row>
     <row r="893" spans="1:5" x14ac:dyDescent="0.35">
@@ -20340,7 +20353,7 @@
         <v>5</v>
       </c>
       <c r="B893" t="s">
-        <v>607</v>
+        <v>498</v>
       </c>
       <c r="C893" t="s">
         <v>14</v>
@@ -20349,7 +20362,7 @@
         <v>8</v>
       </c>
       <c r="E893" t="s">
-        <v>634</v>
+        <v>523</v>
       </c>
     </row>
     <row r="894" spans="1:5" x14ac:dyDescent="0.35">
@@ -20357,7 +20370,7 @@
         <v>5</v>
       </c>
       <c r="B894" t="s">
-        <v>369</v>
+        <v>607</v>
       </c>
       <c r="C894" t="s">
         <v>14</v>
@@ -20366,7 +20379,7 @@
         <v>8</v>
       </c>
       <c r="E894" t="s">
-        <v>396</v>
+        <v>632</v>
       </c>
     </row>
     <row r="895" spans="1:5" x14ac:dyDescent="0.35">
@@ -20374,7 +20387,7 @@
         <v>5</v>
       </c>
       <c r="B895" t="s">
-        <v>275</v>
+        <v>369</v>
       </c>
       <c r="C895" t="s">
         <v>14</v>
@@ -20383,7 +20396,7 @@
         <v>8</v>
       </c>
       <c r="E895" t="s">
-        <v>299</v>
+        <v>394</v>
       </c>
     </row>
     <row r="896" spans="1:5" x14ac:dyDescent="0.35">
@@ -20400,7 +20413,7 @@
         <v>8</v>
       </c>
       <c r="E896" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="897" spans="1:5" x14ac:dyDescent="0.35">
@@ -20417,7 +20430,7 @@
         <v>8</v>
       </c>
       <c r="E897" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="898" spans="1:5" x14ac:dyDescent="0.35">
@@ -20431,10 +20444,10 @@
         <v>14</v>
       </c>
       <c r="D898" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E898" t="s">
-        <v>913</v>
+        <v>943</v>
       </c>
     </row>
     <row r="899" spans="1:5" x14ac:dyDescent="0.35">
@@ -20442,16 +20455,16 @@
         <v>716</v>
       </c>
       <c r="B899" t="s">
-        <v>1127</v>
+        <v>717</v>
       </c>
       <c r="C899" t="s">
         <v>14</v>
       </c>
       <c r="D899" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E899" t="s">
-        <v>1196</v>
+        <v>946</v>
       </c>
     </row>
     <row r="900" spans="1:5" x14ac:dyDescent="0.35">
@@ -20459,16 +20472,16 @@
         <v>716</v>
       </c>
       <c r="B900" t="s">
-        <v>1243</v>
+        <v>1049</v>
       </c>
       <c r="C900" t="s">
         <v>14</v>
       </c>
       <c r="D900" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E900" t="s">
-        <v>1312</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="901" spans="1:5" x14ac:dyDescent="0.35">
@@ -20476,16 +20489,16 @@
         <v>716</v>
       </c>
       <c r="B901" t="s">
-        <v>1359</v>
+        <v>1127</v>
       </c>
       <c r="C901" t="s">
         <v>14</v>
       </c>
       <c r="D901" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E901" t="s">
-        <v>1428</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="902" spans="1:5" x14ac:dyDescent="0.35">
@@ -20493,16 +20506,16 @@
         <v>716</v>
       </c>
       <c r="B902" t="s">
-        <v>1475</v>
+        <v>1127</v>
       </c>
       <c r="C902" t="s">
         <v>14</v>
       </c>
       <c r="D902" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E902" t="s">
-        <v>1545</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="903" spans="1:5" x14ac:dyDescent="0.35">
@@ -20510,16 +20523,16 @@
         <v>716</v>
       </c>
       <c r="B903" t="s">
-        <v>717</v>
+        <v>1243</v>
       </c>
       <c r="C903" t="s">
         <v>14</v>
       </c>
       <c r="D903" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E903" t="s">
-        <v>901</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="904" spans="1:5" x14ac:dyDescent="0.35">
@@ -20527,16 +20540,16 @@
         <v>716</v>
       </c>
       <c r="B904" t="s">
-        <v>717</v>
+        <v>1243</v>
       </c>
       <c r="C904" t="s">
         <v>14</v>
       </c>
       <c r="D904" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E904" t="s">
-        <v>902</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="905" spans="1:5" x14ac:dyDescent="0.35">
@@ -20544,16 +20557,16 @@
         <v>716</v>
       </c>
       <c r="B905" t="s">
-        <v>717</v>
+        <v>1359</v>
       </c>
       <c r="C905" t="s">
         <v>14</v>
       </c>
       <c r="D905" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E905" t="s">
-        <v>903</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="906" spans="1:5" x14ac:dyDescent="0.35">
@@ -20561,16 +20574,16 @@
         <v>716</v>
       </c>
       <c r="B906" t="s">
-        <v>717</v>
+        <v>1359</v>
       </c>
       <c r="C906" t="s">
         <v>14</v>
       </c>
       <c r="D906" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E906" t="s">
-        <v>904</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="907" spans="1:5" x14ac:dyDescent="0.35">
@@ -20578,16 +20591,16 @@
         <v>716</v>
       </c>
       <c r="B907" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C907" t="s">
         <v>14</v>
       </c>
       <c r="D907" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E907" t="s">
-        <v>905</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="908" spans="1:5" x14ac:dyDescent="0.35">
@@ -20595,16 +20608,16 @@
         <v>716</v>
       </c>
       <c r="B908" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C908" t="s">
         <v>14</v>
       </c>
       <c r="D908" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="E908" t="s">
-        <v>906</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="909" spans="1:5" x14ac:dyDescent="0.35">
@@ -20618,10 +20631,10 @@
         <v>14</v>
       </c>
       <c r="D909" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="E909" t="s">
-        <v>907</v>
+        <v>893</v>
       </c>
     </row>
     <row r="910" spans="1:5" x14ac:dyDescent="0.35">
@@ -20635,10 +20648,10 @@
         <v>14</v>
       </c>
       <c r="D910" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="E910" t="s">
-        <v>908</v>
+        <v>894</v>
       </c>
     </row>
     <row r="911" spans="1:5" x14ac:dyDescent="0.35">
@@ -20652,10 +20665,10 @@
         <v>14</v>
       </c>
       <c r="D911" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="E911" t="s">
-        <v>909</v>
+        <v>895</v>
       </c>
     </row>
     <row r="912" spans="1:5" x14ac:dyDescent="0.35">
@@ -20669,10 +20682,10 @@
         <v>14</v>
       </c>
       <c r="D912" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="E912" t="s">
-        <v>910</v>
+        <v>896</v>
       </c>
     </row>
     <row r="913" spans="1:5" x14ac:dyDescent="0.35">
@@ -20686,10 +20699,10 @@
         <v>14</v>
       </c>
       <c r="D913" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="E913" t="s">
-        <v>911</v>
+        <v>897</v>
       </c>
     </row>
     <row r="914" spans="1:5" x14ac:dyDescent="0.35">
@@ -20703,10 +20716,10 @@
         <v>14</v>
       </c>
       <c r="D914" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="E914" t="s">
-        <v>912</v>
+        <v>898</v>
       </c>
     </row>
     <row r="915" spans="1:5" x14ac:dyDescent="0.35">
@@ -20714,16 +20727,16 @@
         <v>716</v>
       </c>
       <c r="B915" t="s">
-        <v>1049</v>
+        <v>717</v>
       </c>
       <c r="C915" t="s">
         <v>14</v>
       </c>
       <c r="D915" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="E915" t="s">
-        <v>1090</v>
+        <v>899</v>
       </c>
     </row>
     <row r="916" spans="1:5" x14ac:dyDescent="0.35">
@@ -20731,16 +20744,16 @@
         <v>716</v>
       </c>
       <c r="B916" t="s">
-        <v>1049</v>
+        <v>717</v>
       </c>
       <c r="C916" t="s">
         <v>14</v>
       </c>
       <c r="D916" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="E916" t="s">
-        <v>1091</v>
+        <v>900</v>
       </c>
     </row>
     <row r="917" spans="1:5" x14ac:dyDescent="0.35">
@@ -20748,7 +20761,7 @@
         <v>716</v>
       </c>
       <c r="B917" t="s">
-        <v>1049</v>
+        <v>717</v>
       </c>
       <c r="C917" t="s">
         <v>14</v>
@@ -20757,7 +20770,7 @@
         <v>45</v>
       </c>
       <c r="E917" t="s">
-        <v>1092</v>
+        <v>901</v>
       </c>
     </row>
     <row r="918" spans="1:5" x14ac:dyDescent="0.35">
@@ -20765,7 +20778,7 @@
         <v>716</v>
       </c>
       <c r="B918" t="s">
-        <v>1049</v>
+        <v>717</v>
       </c>
       <c r="C918" t="s">
         <v>14</v>
@@ -20774,7 +20787,7 @@
         <v>45</v>
       </c>
       <c r="E918" t="s">
-        <v>1093</v>
+        <v>902</v>
       </c>
     </row>
     <row r="919" spans="1:5" x14ac:dyDescent="0.35">
@@ -20782,7 +20795,7 @@
         <v>716</v>
       </c>
       <c r="B919" t="s">
-        <v>1049</v>
+        <v>717</v>
       </c>
       <c r="C919" t="s">
         <v>14</v>
@@ -20791,7 +20804,7 @@
         <v>45</v>
       </c>
       <c r="E919" t="s">
-        <v>1094</v>
+        <v>903</v>
       </c>
     </row>
     <row r="920" spans="1:5" x14ac:dyDescent="0.35">
@@ -20799,7 +20812,7 @@
         <v>716</v>
       </c>
       <c r="B920" t="s">
-        <v>1127</v>
+        <v>717</v>
       </c>
       <c r="C920" t="s">
         <v>14</v>
@@ -20808,7 +20821,7 @@
         <v>45</v>
       </c>
       <c r="E920" t="s">
-        <v>1190</v>
+        <v>904</v>
       </c>
     </row>
     <row r="921" spans="1:5" x14ac:dyDescent="0.35">
@@ -20816,7 +20829,7 @@
         <v>716</v>
       </c>
       <c r="B921" t="s">
-        <v>1127</v>
+        <v>717</v>
       </c>
       <c r="C921" t="s">
         <v>14</v>
@@ -20825,7 +20838,7 @@
         <v>45</v>
       </c>
       <c r="E921" t="s">
-        <v>1191</v>
+        <v>905</v>
       </c>
     </row>
     <row r="922" spans="1:5" x14ac:dyDescent="0.35">
@@ -20833,7 +20846,7 @@
         <v>716</v>
       </c>
       <c r="B922" t="s">
-        <v>1127</v>
+        <v>717</v>
       </c>
       <c r="C922" t="s">
         <v>14</v>
@@ -20842,7 +20855,7 @@
         <v>45</v>
       </c>
       <c r="E922" t="s">
-        <v>1192</v>
+        <v>906</v>
       </c>
     </row>
     <row r="923" spans="1:5" x14ac:dyDescent="0.35">
@@ -20850,7 +20863,7 @@
         <v>716</v>
       </c>
       <c r="B923" t="s">
-        <v>1127</v>
+        <v>717</v>
       </c>
       <c r="C923" t="s">
         <v>14</v>
@@ -20859,7 +20872,7 @@
         <v>45</v>
       </c>
       <c r="E923" t="s">
-        <v>1193</v>
+        <v>907</v>
       </c>
     </row>
     <row r="924" spans="1:5" x14ac:dyDescent="0.35">
@@ -20867,7 +20880,7 @@
         <v>716</v>
       </c>
       <c r="B924" t="s">
-        <v>1127</v>
+        <v>717</v>
       </c>
       <c r="C924" t="s">
         <v>14</v>
@@ -20876,7 +20889,7 @@
         <v>45</v>
       </c>
       <c r="E924" t="s">
-        <v>1194</v>
+        <v>908</v>
       </c>
     </row>
     <row r="925" spans="1:5" x14ac:dyDescent="0.35">
@@ -20884,7 +20897,7 @@
         <v>716</v>
       </c>
       <c r="B925" t="s">
-        <v>1127</v>
+        <v>717</v>
       </c>
       <c r="C925" t="s">
         <v>14</v>
@@ -20893,7 +20906,7 @@
         <v>45</v>
       </c>
       <c r="E925" t="s">
-        <v>1195</v>
+        <v>909</v>
       </c>
     </row>
     <row r="926" spans="1:5" x14ac:dyDescent="0.35">
@@ -20901,7 +20914,7 @@
         <v>716</v>
       </c>
       <c r="B926" t="s">
-        <v>1243</v>
+        <v>717</v>
       </c>
       <c r="C926" t="s">
         <v>14</v>
@@ -20910,7 +20923,7 @@
         <v>45</v>
       </c>
       <c r="E926" t="s">
-        <v>1306</v>
+        <v>910</v>
       </c>
     </row>
     <row r="927" spans="1:5" x14ac:dyDescent="0.35">
@@ -20918,7 +20931,7 @@
         <v>716</v>
       </c>
       <c r="B927" t="s">
-        <v>1243</v>
+        <v>717</v>
       </c>
       <c r="C927" t="s">
         <v>14</v>
@@ -20927,7 +20940,7 @@
         <v>45</v>
       </c>
       <c r="E927" t="s">
-        <v>1307</v>
+        <v>911</v>
       </c>
     </row>
     <row r="928" spans="1:5" x14ac:dyDescent="0.35">
@@ -20935,7 +20948,7 @@
         <v>716</v>
       </c>
       <c r="B928" t="s">
-        <v>1243</v>
+        <v>717</v>
       </c>
       <c r="C928" t="s">
         <v>14</v>
@@ -20944,7 +20957,7 @@
         <v>45</v>
       </c>
       <c r="E928" t="s">
-        <v>1308</v>
+        <v>912</v>
       </c>
     </row>
     <row r="929" spans="1:5" x14ac:dyDescent="0.35">
@@ -20952,16 +20965,16 @@
         <v>716</v>
       </c>
       <c r="B929" t="s">
-        <v>1243</v>
+        <v>717</v>
       </c>
       <c r="C929" t="s">
         <v>14</v>
       </c>
       <c r="D929" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E929" t="s">
-        <v>1309</v>
+        <v>927</v>
       </c>
     </row>
     <row r="930" spans="1:5" x14ac:dyDescent="0.35">
@@ -20969,16 +20982,16 @@
         <v>716</v>
       </c>
       <c r="B930" t="s">
-        <v>1243</v>
+        <v>717</v>
       </c>
       <c r="C930" t="s">
         <v>14</v>
       </c>
       <c r="D930" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E930" t="s">
-        <v>1310</v>
+        <v>914</v>
       </c>
     </row>
     <row r="931" spans="1:5" x14ac:dyDescent="0.35">
@@ -20986,16 +20999,16 @@
         <v>716</v>
       </c>
       <c r="B931" t="s">
-        <v>1243</v>
+        <v>717</v>
       </c>
       <c r="C931" t="s">
         <v>14</v>
       </c>
       <c r="D931" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E931" t="s">
-        <v>1311</v>
+        <v>915</v>
       </c>
     </row>
     <row r="932" spans="1:5" x14ac:dyDescent="0.35">
@@ -21003,16 +21016,16 @@
         <v>716</v>
       </c>
       <c r="B932" t="s">
-        <v>1359</v>
+        <v>717</v>
       </c>
       <c r="C932" t="s">
         <v>14</v>
       </c>
       <c r="D932" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E932" t="s">
-        <v>1422</v>
+        <v>916</v>
       </c>
     </row>
     <row r="933" spans="1:5" x14ac:dyDescent="0.35">
@@ -21020,16 +21033,16 @@
         <v>716</v>
       </c>
       <c r="B933" t="s">
-        <v>1359</v>
+        <v>717</v>
       </c>
       <c r="C933" t="s">
         <v>14</v>
       </c>
       <c r="D933" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E933" t="s">
-        <v>1423</v>
+        <v>917</v>
       </c>
     </row>
     <row r="934" spans="1:5" x14ac:dyDescent="0.35">
@@ -21037,16 +21050,16 @@
         <v>716</v>
       </c>
       <c r="B934" t="s">
-        <v>1359</v>
+        <v>717</v>
       </c>
       <c r="C934" t="s">
         <v>14</v>
       </c>
       <c r="D934" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E934" t="s">
-        <v>1424</v>
+        <v>918</v>
       </c>
     </row>
     <row r="935" spans="1:5" x14ac:dyDescent="0.35">
@@ -21054,16 +21067,16 @@
         <v>716</v>
       </c>
       <c r="B935" t="s">
-        <v>1359</v>
+        <v>717</v>
       </c>
       <c r="C935" t="s">
         <v>14</v>
       </c>
       <c r="D935" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E935" t="s">
-        <v>1425</v>
+        <v>919</v>
       </c>
     </row>
     <row r="936" spans="1:5" x14ac:dyDescent="0.35">
@@ -21071,16 +21084,16 @@
         <v>716</v>
       </c>
       <c r="B936" t="s">
-        <v>1359</v>
+        <v>717</v>
       </c>
       <c r="C936" t="s">
         <v>14</v>
       </c>
       <c r="D936" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E936" t="s">
-        <v>1426</v>
+        <v>920</v>
       </c>
     </row>
     <row r="937" spans="1:5" x14ac:dyDescent="0.35">
@@ -21088,16 +21101,16 @@
         <v>716</v>
       </c>
       <c r="B937" t="s">
-        <v>1359</v>
+        <v>717</v>
       </c>
       <c r="C937" t="s">
         <v>14</v>
       </c>
       <c r="D937" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E937" t="s">
-        <v>1427</v>
+        <v>921</v>
       </c>
     </row>
     <row r="938" spans="1:5" x14ac:dyDescent="0.35">
@@ -21105,16 +21118,16 @@
         <v>716</v>
       </c>
       <c r="B938" t="s">
-        <v>1475</v>
+        <v>717</v>
       </c>
       <c r="C938" t="s">
         <v>14</v>
       </c>
       <c r="D938" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E938" t="s">
-        <v>1539</v>
+        <v>922</v>
       </c>
     </row>
     <row r="939" spans="1:5" x14ac:dyDescent="0.35">
@@ -21122,16 +21135,16 @@
         <v>716</v>
       </c>
       <c r="B939" t="s">
-        <v>1475</v>
+        <v>717</v>
       </c>
       <c r="C939" t="s">
         <v>14</v>
       </c>
       <c r="D939" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E939" t="s">
-        <v>1540</v>
+        <v>923</v>
       </c>
     </row>
     <row r="940" spans="1:5" x14ac:dyDescent="0.35">
@@ -21139,16 +21152,16 @@
         <v>716</v>
       </c>
       <c r="B940" t="s">
-        <v>1475</v>
+        <v>717</v>
       </c>
       <c r="C940" t="s">
         <v>14</v>
       </c>
       <c r="D940" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E940" t="s">
-        <v>1541</v>
+        <v>924</v>
       </c>
     </row>
     <row r="941" spans="1:5" x14ac:dyDescent="0.35">
@@ -21156,16 +21169,16 @@
         <v>716</v>
       </c>
       <c r="B941" t="s">
-        <v>1475</v>
+        <v>717</v>
       </c>
       <c r="C941" t="s">
         <v>14</v>
       </c>
       <c r="D941" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E941" t="s">
-        <v>1542</v>
+        <v>925</v>
       </c>
     </row>
     <row r="942" spans="1:5" x14ac:dyDescent="0.35">
@@ -21173,16 +21186,16 @@
         <v>716</v>
       </c>
       <c r="B942" t="s">
-        <v>1475</v>
+        <v>717</v>
       </c>
       <c r="C942" t="s">
         <v>14</v>
       </c>
       <c r="D942" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E942" t="s">
-        <v>1543</v>
+        <v>926</v>
       </c>
     </row>
     <row r="943" spans="1:5" x14ac:dyDescent="0.35">
@@ -21190,16 +21203,16 @@
         <v>716</v>
       </c>
       <c r="B943" t="s">
-        <v>1475</v>
+        <v>717</v>
       </c>
       <c r="C943" t="s">
         <v>14</v>
       </c>
       <c r="D943" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E943" t="s">
-        <v>1544</v>
+        <v>928</v>
       </c>
     </row>
     <row r="944" spans="1:5" x14ac:dyDescent="0.35">
@@ -21213,10 +21226,10 @@
         <v>14</v>
       </c>
       <c r="D944" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E944" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
     </row>
     <row r="945" spans="1:5" x14ac:dyDescent="0.35">
@@ -21230,10 +21243,10 @@
         <v>14</v>
       </c>
       <c r="D945" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E945" t="s">
-        <v>914</v>
+        <v>930</v>
       </c>
     </row>
     <row r="946" spans="1:5" x14ac:dyDescent="0.35">
@@ -21247,10 +21260,10 @@
         <v>14</v>
       </c>
       <c r="D946" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E946" t="s">
-        <v>915</v>
+        <v>931</v>
       </c>
     </row>
     <row r="947" spans="1:5" x14ac:dyDescent="0.35">
@@ -21264,10 +21277,10 @@
         <v>14</v>
       </c>
       <c r="D947" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E947" t="s">
-        <v>916</v>
+        <v>932</v>
       </c>
     </row>
     <row r="948" spans="1:5" x14ac:dyDescent="0.35">
@@ -21281,10 +21294,10 @@
         <v>14</v>
       </c>
       <c r="D948" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E948" t="s">
-        <v>917</v>
+        <v>933</v>
       </c>
     </row>
     <row r="949" spans="1:5" x14ac:dyDescent="0.35">
@@ -21298,10 +21311,10 @@
         <v>14</v>
       </c>
       <c r="D949" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E949" t="s">
-        <v>918</v>
+        <v>934</v>
       </c>
     </row>
     <row r="950" spans="1:5" x14ac:dyDescent="0.35">
@@ -21315,10 +21328,10 @@
         <v>14</v>
       </c>
       <c r="D950" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E950" t="s">
-        <v>919</v>
+        <v>935</v>
       </c>
     </row>
     <row r="951" spans="1:5" x14ac:dyDescent="0.35">
@@ -21332,10 +21345,10 @@
         <v>14</v>
       </c>
       <c r="D951" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E951" t="s">
-        <v>920</v>
+        <v>936</v>
       </c>
     </row>
     <row r="952" spans="1:5" x14ac:dyDescent="0.35">
@@ -21349,10 +21362,10 @@
         <v>14</v>
       </c>
       <c r="D952" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E952" t="s">
-        <v>921</v>
+        <v>937</v>
       </c>
     </row>
     <row r="953" spans="1:5" x14ac:dyDescent="0.35">
@@ -21366,10 +21379,10 @@
         <v>14</v>
       </c>
       <c r="D953" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E953" t="s">
-        <v>922</v>
+        <v>950</v>
       </c>
     </row>
     <row r="954" spans="1:5" x14ac:dyDescent="0.35">
@@ -21383,10 +21396,10 @@
         <v>14</v>
       </c>
       <c r="D954" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E954" t="s">
-        <v>923</v>
+        <v>959</v>
       </c>
     </row>
     <row r="955" spans="1:5" x14ac:dyDescent="0.35">
@@ -21400,10 +21413,10 @@
         <v>14</v>
       </c>
       <c r="D955" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E955" t="s">
-        <v>924</v>
+        <v>960</v>
       </c>
     </row>
     <row r="956" spans="1:5" x14ac:dyDescent="0.35">
@@ -21417,10 +21430,10 @@
         <v>14</v>
       </c>
       <c r="D956" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E956" t="s">
-        <v>925</v>
+        <v>961</v>
       </c>
     </row>
     <row r="957" spans="1:5" x14ac:dyDescent="0.35">
@@ -21434,10 +21447,10 @@
         <v>14</v>
       </c>
       <c r="D957" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E957" t="s">
-        <v>926</v>
+        <v>962</v>
       </c>
     </row>
     <row r="958" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
@@ -23315,16 +23328,16 @@
         <v>716</v>
       </c>
       <c r="B1068" t="s">
-        <v>1049</v>
+        <v>717</v>
       </c>
       <c r="C1068" t="s">
         <v>14</v>
       </c>
       <c r="D1068" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E1068" t="s">
-        <v>1095</v>
+        <v>963</v>
       </c>
     </row>
     <row r="1069" spans="1:5" x14ac:dyDescent="0.35">
@@ -23332,16 +23345,16 @@
         <v>716</v>
       </c>
       <c r="B1069" t="s">
-        <v>1049</v>
+        <v>717</v>
       </c>
       <c r="C1069" t="s">
         <v>14</v>
       </c>
       <c r="D1069" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E1069" t="s">
-        <v>1096</v>
+        <v>964</v>
       </c>
     </row>
     <row r="1070" spans="1:5" x14ac:dyDescent="0.35">
@@ -23349,16 +23362,16 @@
         <v>716</v>
       </c>
       <c r="B1070" t="s">
-        <v>1049</v>
+        <v>717</v>
       </c>
       <c r="C1070" t="s">
         <v>14</v>
       </c>
       <c r="D1070" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E1070" t="s">
-        <v>1097</v>
+        <v>965</v>
       </c>
     </row>
     <row r="1071" spans="1:5" x14ac:dyDescent="0.35">
@@ -23366,16 +23379,16 @@
         <v>716</v>
       </c>
       <c r="B1071" t="s">
-        <v>1049</v>
+        <v>717</v>
       </c>
       <c r="C1071" t="s">
         <v>14</v>
       </c>
       <c r="D1071" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E1071" t="s">
-        <v>1098</v>
+        <v>966</v>
       </c>
     </row>
     <row r="1072" spans="1:5" x14ac:dyDescent="0.35">
@@ -23383,16 +23396,16 @@
         <v>716</v>
       </c>
       <c r="B1072" t="s">
-        <v>1049</v>
+        <v>717</v>
       </c>
       <c r="C1072" t="s">
         <v>14</v>
       </c>
       <c r="D1072" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E1072" t="s">
-        <v>1099</v>
+        <v>967</v>
       </c>
     </row>
     <row r="1073" spans="1:5" x14ac:dyDescent="0.35">
@@ -23400,16 +23413,16 @@
         <v>716</v>
       </c>
       <c r="B1073" t="s">
-        <v>1127</v>
+        <v>717</v>
       </c>
       <c r="C1073" t="s">
         <v>14</v>
       </c>
       <c r="D1073" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E1073" t="s">
-        <v>1197</v>
+        <v>968</v>
       </c>
     </row>
     <row r="1074" spans="1:5" x14ac:dyDescent="0.35">
@@ -23417,16 +23430,16 @@
         <v>716</v>
       </c>
       <c r="B1074" t="s">
-        <v>1127</v>
+        <v>717</v>
       </c>
       <c r="C1074" t="s">
         <v>14</v>
       </c>
       <c r="D1074" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E1074" t="s">
-        <v>1198</v>
+        <v>951</v>
       </c>
     </row>
     <row r="1075" spans="1:5" x14ac:dyDescent="0.35">
@@ -23434,16 +23447,16 @@
         <v>716</v>
       </c>
       <c r="B1075" t="s">
-        <v>1127</v>
+        <v>717</v>
       </c>
       <c r="C1075" t="s">
         <v>14</v>
       </c>
       <c r="D1075" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E1075" t="s">
-        <v>1199</v>
+        <v>952</v>
       </c>
     </row>
     <row r="1076" spans="1:5" x14ac:dyDescent="0.35">
@@ -23451,16 +23464,16 @@
         <v>716</v>
       </c>
       <c r="B1076" t="s">
-        <v>1127</v>
+        <v>717</v>
       </c>
       <c r="C1076" t="s">
         <v>14</v>
       </c>
       <c r="D1076" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E1076" t="s">
-        <v>1200</v>
+        <v>953</v>
       </c>
     </row>
     <row r="1077" spans="1:5" x14ac:dyDescent="0.35">
@@ -23468,16 +23481,16 @@
         <v>716</v>
       </c>
       <c r="B1077" t="s">
-        <v>1127</v>
+        <v>717</v>
       </c>
       <c r="C1077" t="s">
         <v>14</v>
       </c>
       <c r="D1077" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E1077" t="s">
-        <v>1201</v>
+        <v>954</v>
       </c>
     </row>
     <row r="1078" spans="1:5" x14ac:dyDescent="0.35">
@@ -23485,16 +23498,16 @@
         <v>716</v>
       </c>
       <c r="B1078" t="s">
-        <v>1127</v>
+        <v>717</v>
       </c>
       <c r="C1078" t="s">
         <v>14</v>
       </c>
       <c r="D1078" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E1078" t="s">
-        <v>1202</v>
+        <v>969</v>
       </c>
     </row>
     <row r="1079" spans="1:5" x14ac:dyDescent="0.35">
@@ -23502,16 +23515,16 @@
         <v>716</v>
       </c>
       <c r="B1079" t="s">
-        <v>1127</v>
+        <v>717</v>
       </c>
       <c r="C1079" t="s">
         <v>14</v>
       </c>
       <c r="D1079" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E1079" t="s">
-        <v>1203</v>
+        <v>970</v>
       </c>
     </row>
     <row r="1080" spans="1:5" x14ac:dyDescent="0.35">
@@ -23519,16 +23532,16 @@
         <v>716</v>
       </c>
       <c r="B1080" t="s">
-        <v>1243</v>
+        <v>717</v>
       </c>
       <c r="C1080" t="s">
         <v>14</v>
       </c>
       <c r="D1080" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E1080" t="s">
-        <v>1313</v>
+        <v>971</v>
       </c>
     </row>
     <row r="1081" spans="1:5" x14ac:dyDescent="0.35">
@@ -23536,16 +23549,16 @@
         <v>716</v>
       </c>
       <c r="B1081" t="s">
-        <v>1243</v>
+        <v>717</v>
       </c>
       <c r="C1081" t="s">
         <v>14</v>
       </c>
       <c r="D1081" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E1081" t="s">
-        <v>1314</v>
+        <v>972</v>
       </c>
     </row>
     <row r="1082" spans="1:5" x14ac:dyDescent="0.35">
@@ -23553,16 +23566,16 @@
         <v>716</v>
       </c>
       <c r="B1082" t="s">
-        <v>1243</v>
+        <v>717</v>
       </c>
       <c r="C1082" t="s">
         <v>14</v>
       </c>
       <c r="D1082" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E1082" t="s">
-        <v>1315</v>
+        <v>955</v>
       </c>
     </row>
     <row r="1083" spans="1:5" x14ac:dyDescent="0.35">
@@ -23570,16 +23583,16 @@
         <v>716</v>
       </c>
       <c r="B1083" t="s">
-        <v>1243</v>
+        <v>717</v>
       </c>
       <c r="C1083" t="s">
         <v>14</v>
       </c>
       <c r="D1083" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E1083" t="s">
-        <v>1316</v>
+        <v>956</v>
       </c>
     </row>
     <row r="1084" spans="1:5" x14ac:dyDescent="0.35">
@@ -23587,16 +23600,16 @@
         <v>716</v>
       </c>
       <c r="B1084" t="s">
-        <v>1243</v>
+        <v>717</v>
       </c>
       <c r="C1084" t="s">
         <v>14</v>
       </c>
       <c r="D1084" t="s">
-        <v>48</v>
+        <v>794</v>
       </c>
       <c r="E1084" t="s">
-        <v>1317</v>
+        <v>957</v>
       </c>
     </row>
     <row r="1085" spans="1:5" x14ac:dyDescent="0.35">
@@ -23604,16 +23617,16 @@
         <v>716</v>
       </c>
       <c r="B1085" t="s">
-        <v>1243</v>
+        <v>717</v>
       </c>
       <c r="C1085" t="s">
         <v>14</v>
       </c>
       <c r="D1085" t="s">
-        <v>48</v>
+        <v>802</v>
       </c>
       <c r="E1085" t="s">
-        <v>1318</v>
+        <v>973</v>
       </c>
     </row>
     <row r="1086" spans="1:5" x14ac:dyDescent="0.35">
@@ -23621,16 +23634,16 @@
         <v>716</v>
       </c>
       <c r="B1086" t="s">
-        <v>1243</v>
+        <v>717</v>
       </c>
       <c r="C1086" t="s">
         <v>14</v>
       </c>
       <c r="D1086" t="s">
-        <v>48</v>
+        <v>802</v>
       </c>
       <c r="E1086" t="s">
-        <v>1319</v>
+        <v>974</v>
       </c>
     </row>
     <row r="1087" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
@@ -24981,16 +24994,16 @@
         <v>716</v>
       </c>
       <c r="B1166" t="s">
-        <v>1359</v>
+        <v>717</v>
       </c>
       <c r="C1166" t="s">
         <v>14</v>
       </c>
       <c r="D1166" t="s">
-        <v>48</v>
+        <v>802</v>
       </c>
       <c r="E1166" t="s">
-        <v>1429</v>
+        <v>975</v>
       </c>
     </row>
     <row r="1167" spans="1:5" x14ac:dyDescent="0.35">
@@ -24998,16 +25011,16 @@
         <v>716</v>
       </c>
       <c r="B1167" t="s">
-        <v>1359</v>
+        <v>717</v>
       </c>
       <c r="C1167" t="s">
         <v>14</v>
       </c>
       <c r="D1167" t="s">
-        <v>48</v>
+        <v>802</v>
       </c>
       <c r="E1167" t="s">
-        <v>1430</v>
+        <v>976</v>
       </c>
     </row>
     <row r="1168" spans="1:5" x14ac:dyDescent="0.35">
@@ -25015,16 +25028,16 @@
         <v>716</v>
       </c>
       <c r="B1168" t="s">
-        <v>1359</v>
+        <v>717</v>
       </c>
       <c r="C1168" t="s">
         <v>14</v>
       </c>
       <c r="D1168" t="s">
-        <v>48</v>
+        <v>802</v>
       </c>
       <c r="E1168" t="s">
-        <v>1431</v>
+        <v>977</v>
       </c>
     </row>
     <row r="1169" spans="1:5" x14ac:dyDescent="0.35">
@@ -25032,16 +25045,16 @@
         <v>716</v>
       </c>
       <c r="B1169" t="s">
-        <v>1359</v>
+        <v>717</v>
       </c>
       <c r="C1169" t="s">
         <v>14</v>
       </c>
       <c r="D1169" t="s">
-        <v>48</v>
+        <v>802</v>
       </c>
       <c r="E1169" t="s">
-        <v>1432</v>
+        <v>978</v>
       </c>
     </row>
     <row r="1170" spans="1:5" x14ac:dyDescent="0.35">
@@ -25049,16 +25062,16 @@
         <v>716</v>
       </c>
       <c r="B1170" t="s">
-        <v>1359</v>
+        <v>717</v>
       </c>
       <c r="C1170" t="s">
         <v>14</v>
       </c>
       <c r="D1170" t="s">
-        <v>48</v>
+        <v>802</v>
       </c>
       <c r="E1170" t="s">
-        <v>1433</v>
+        <v>979</v>
       </c>
     </row>
     <row r="1171" spans="1:5" x14ac:dyDescent="0.35">
@@ -25066,16 +25079,16 @@
         <v>716</v>
       </c>
       <c r="B1171" t="s">
-        <v>1359</v>
+        <v>717</v>
       </c>
       <c r="C1171" t="s">
         <v>14</v>
       </c>
       <c r="D1171" t="s">
-        <v>48</v>
+        <v>802</v>
       </c>
       <c r="E1171" t="s">
-        <v>1434</v>
+        <v>980</v>
       </c>
     </row>
     <row r="1172" spans="1:5" x14ac:dyDescent="0.35">
@@ -25083,16 +25096,16 @@
         <v>716</v>
       </c>
       <c r="B1172" t="s">
-        <v>1359</v>
+        <v>717</v>
       </c>
       <c r="C1172" t="s">
         <v>14</v>
       </c>
       <c r="D1172" t="s">
-        <v>48</v>
+        <v>802</v>
       </c>
       <c r="E1172" t="s">
-        <v>1435</v>
+        <v>981</v>
       </c>
     </row>
     <row r="1173" spans="1:5" x14ac:dyDescent="0.35">
@@ -25100,16 +25113,16 @@
         <v>716</v>
       </c>
       <c r="B1173" t="s">
-        <v>1475</v>
+        <v>717</v>
       </c>
       <c r="C1173" t="s">
         <v>14</v>
       </c>
       <c r="D1173" t="s">
-        <v>48</v>
+        <v>802</v>
       </c>
       <c r="E1173" t="s">
-        <v>1546</v>
+        <v>982</v>
       </c>
     </row>
     <row r="1174" spans="1:5" x14ac:dyDescent="0.35">
@@ -25117,16 +25130,16 @@
         <v>716</v>
       </c>
       <c r="B1174" t="s">
-        <v>1475</v>
+        <v>1049</v>
       </c>
       <c r="C1174" t="s">
         <v>14</v>
       </c>
       <c r="D1174" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E1174" t="s">
-        <v>1547</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="1175" spans="1:5" x14ac:dyDescent="0.35">
@@ -25134,16 +25147,16 @@
         <v>716</v>
       </c>
       <c r="B1175" t="s">
-        <v>1475</v>
+        <v>1049</v>
       </c>
       <c r="C1175" t="s">
         <v>14</v>
       </c>
       <c r="D1175" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E1175" t="s">
-        <v>1548</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="1176" spans="1:5" x14ac:dyDescent="0.35">
@@ -25151,16 +25164,16 @@
         <v>716</v>
       </c>
       <c r="B1176" t="s">
-        <v>1475</v>
+        <v>1049</v>
       </c>
       <c r="C1176" t="s">
         <v>14</v>
       </c>
       <c r="D1176" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E1176" t="s">
-        <v>1549</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="1177" spans="1:5" x14ac:dyDescent="0.35">
@@ -25168,16 +25181,16 @@
         <v>716</v>
       </c>
       <c r="B1177" t="s">
-        <v>1475</v>
+        <v>1049</v>
       </c>
       <c r="C1177" t="s">
         <v>14</v>
       </c>
       <c r="D1177" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="E1177" t="s">
-        <v>1550</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="1178" spans="1:5" x14ac:dyDescent="0.35">
@@ -25185,16 +25198,16 @@
         <v>716</v>
       </c>
       <c r="B1178" t="s">
-        <v>1475</v>
+        <v>1049</v>
       </c>
       <c r="C1178" t="s">
         <v>14</v>
       </c>
       <c r="D1178" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E1178" t="s">
-        <v>1551</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="1179" spans="1:5" x14ac:dyDescent="0.35">
@@ -25202,16 +25215,16 @@
         <v>716</v>
       </c>
       <c r="B1179" t="s">
-        <v>1475</v>
+        <v>1049</v>
       </c>
       <c r="C1179" t="s">
         <v>14</v>
       </c>
       <c r="D1179" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E1179" t="s">
-        <v>1552</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="1180" spans="1:5" x14ac:dyDescent="0.35">
@@ -25219,16 +25232,16 @@
         <v>716</v>
       </c>
       <c r="B1180" t="s">
-        <v>717</v>
+        <v>1049</v>
       </c>
       <c r="C1180" t="s">
         <v>14</v>
       </c>
       <c r="D1180" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E1180" t="s">
-        <v>928</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="1181" spans="1:5" x14ac:dyDescent="0.35">
@@ -25236,16 +25249,16 @@
         <v>716</v>
       </c>
       <c r="B1181" t="s">
-        <v>717</v>
+        <v>1049</v>
       </c>
       <c r="C1181" t="s">
         <v>14</v>
       </c>
       <c r="D1181" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E1181" t="s">
-        <v>929</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="1182" spans="1:5" x14ac:dyDescent="0.35">
@@ -25253,16 +25266,16 @@
         <v>716</v>
       </c>
       <c r="B1182" t="s">
-        <v>717</v>
+        <v>1049</v>
       </c>
       <c r="C1182" t="s">
         <v>14</v>
       </c>
       <c r="D1182" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E1182" t="s">
-        <v>930</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="1183" spans="1:5" x14ac:dyDescent="0.35">
@@ -25270,16 +25283,16 @@
         <v>716</v>
       </c>
       <c r="B1183" t="s">
-        <v>717</v>
+        <v>1049</v>
       </c>
       <c r="C1183" t="s">
         <v>14</v>
       </c>
       <c r="D1183" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E1183" t="s">
-        <v>931</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="1184" spans="1:5" x14ac:dyDescent="0.35">
@@ -25287,16 +25300,16 @@
         <v>716</v>
       </c>
       <c r="B1184" t="s">
-        <v>717</v>
+        <v>1049</v>
       </c>
       <c r="C1184" t="s">
         <v>14</v>
       </c>
       <c r="D1184" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E1184" t="s">
-        <v>932</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="1185" spans="1:5" x14ac:dyDescent="0.35">
@@ -25304,16 +25317,16 @@
         <v>716</v>
       </c>
       <c r="B1185" t="s">
-        <v>717</v>
+        <v>1049</v>
       </c>
       <c r="C1185" t="s">
         <v>14</v>
       </c>
       <c r="D1185" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E1185" t="s">
-        <v>933</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="1186" spans="1:5" x14ac:dyDescent="0.35">
@@ -25321,16 +25334,16 @@
         <v>716</v>
       </c>
       <c r="B1186" t="s">
-        <v>717</v>
+        <v>1049</v>
       </c>
       <c r="C1186" t="s">
         <v>14</v>
       </c>
       <c r="D1186" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E1186" t="s">
-        <v>934</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="1187" spans="1:5" x14ac:dyDescent="0.35">
@@ -25338,16 +25351,16 @@
         <v>716</v>
       </c>
       <c r="B1187" t="s">
-        <v>717</v>
+        <v>1049</v>
       </c>
       <c r="C1187" t="s">
         <v>14</v>
       </c>
       <c r="D1187" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E1187" t="s">
-        <v>935</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="1188" spans="1:5" x14ac:dyDescent="0.35">
@@ -25355,16 +25368,16 @@
         <v>716</v>
       </c>
       <c r="B1188" t="s">
-        <v>717</v>
+        <v>1127</v>
       </c>
       <c r="C1188" t="s">
         <v>14</v>
       </c>
       <c r="D1188" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E1188" t="s">
-        <v>936</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="1189" spans="1:5" x14ac:dyDescent="0.35">
@@ -25372,16 +25385,16 @@
         <v>716</v>
       </c>
       <c r="B1189" t="s">
-        <v>717</v>
+        <v>1127</v>
       </c>
       <c r="C1189" t="s">
         <v>14</v>
       </c>
       <c r="D1189" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="E1189" t="s">
-        <v>937</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="1190" spans="1:5" x14ac:dyDescent="0.35">
@@ -25389,16 +25402,16 @@
         <v>716</v>
       </c>
       <c r="B1190" t="s">
-        <v>717</v>
+        <v>1127</v>
       </c>
       <c r="C1190" t="s">
         <v>14</v>
       </c>
       <c r="D1190" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="E1190" t="s">
-        <v>938</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="1191" spans="1:5" x14ac:dyDescent="0.35">
@@ -25406,16 +25419,16 @@
         <v>716</v>
       </c>
       <c r="B1191" t="s">
-        <v>717</v>
+        <v>1127</v>
       </c>
       <c r="C1191" t="s">
         <v>14</v>
       </c>
       <c r="D1191" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="E1191" t="s">
-        <v>941</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="1192" spans="1:5" x14ac:dyDescent="0.35">
@@ -25423,16 +25436,16 @@
         <v>716</v>
       </c>
       <c r="B1192" t="s">
-        <v>717</v>
+        <v>1127</v>
       </c>
       <c r="C1192" t="s">
         <v>14</v>
       </c>
       <c r="D1192" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="E1192" t="s">
-        <v>944</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="1193" spans="1:5" x14ac:dyDescent="0.35">
@@ -25440,16 +25453,16 @@
         <v>716</v>
       </c>
       <c r="B1193" t="s">
-        <v>1049</v>
+        <v>1127</v>
       </c>
       <c r="C1193" t="s">
         <v>14</v>
       </c>
       <c r="D1193" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E1193" t="s">
-        <v>1100</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="1194" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
@@ -26942,10 +26955,10 @@
         <v>14</v>
       </c>
       <c r="D1281" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E1281" t="s">
-        <v>1204</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="1282" spans="1:5" x14ac:dyDescent="0.35">
@@ -26959,10 +26972,10 @@
         <v>14</v>
       </c>
       <c r="D1282" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E1282" t="s">
-        <v>1207</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="1283" spans="1:5" x14ac:dyDescent="0.35">
@@ -26976,10 +26989,10 @@
         <v>14</v>
       </c>
       <c r="D1283" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E1283" t="s">
-        <v>1210</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="1284" spans="1:5" x14ac:dyDescent="0.35">
@@ -26987,16 +27000,16 @@
         <v>716</v>
       </c>
       <c r="B1284" t="s">
-        <v>1243</v>
+        <v>1127</v>
       </c>
       <c r="C1284" t="s">
         <v>14</v>
       </c>
       <c r="D1284" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E1284" t="s">
-        <v>1320</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="1285" spans="1:5" x14ac:dyDescent="0.35">
@@ -27004,16 +27017,16 @@
         <v>716</v>
       </c>
       <c r="B1285" t="s">
-        <v>1243</v>
+        <v>1127</v>
       </c>
       <c r="C1285" t="s">
         <v>14</v>
       </c>
       <c r="D1285" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E1285" t="s">
-        <v>1323</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="1286" spans="1:5" x14ac:dyDescent="0.35">
@@ -27021,16 +27034,16 @@
         <v>716</v>
       </c>
       <c r="B1286" t="s">
-        <v>1243</v>
+        <v>1127</v>
       </c>
       <c r="C1286" t="s">
         <v>14</v>
       </c>
       <c r="D1286" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E1286" t="s">
-        <v>1326</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="1287" spans="1:5" x14ac:dyDescent="0.35">
@@ -27038,16 +27051,16 @@
         <v>716</v>
       </c>
       <c r="B1287" t="s">
-        <v>1359</v>
+        <v>1127</v>
       </c>
       <c r="C1287" t="s">
         <v>14</v>
       </c>
       <c r="D1287" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E1287" t="s">
-        <v>1436</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="1288" spans="1:5" x14ac:dyDescent="0.35">
@@ -27055,16 +27068,16 @@
         <v>716</v>
       </c>
       <c r="B1288" t="s">
-        <v>1359</v>
+        <v>1127</v>
       </c>
       <c r="C1288" t="s">
         <v>14</v>
       </c>
       <c r="D1288" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E1288" t="s">
-        <v>1439</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="1289" spans="1:5" x14ac:dyDescent="0.35">
@@ -27072,16 +27085,16 @@
         <v>716</v>
       </c>
       <c r="B1289" t="s">
-        <v>1359</v>
+        <v>1127</v>
       </c>
       <c r="C1289" t="s">
         <v>14</v>
       </c>
       <c r="D1289" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E1289" t="s">
-        <v>1442</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="1290" spans="1:5" x14ac:dyDescent="0.35">
@@ -27089,16 +27102,16 @@
         <v>716</v>
       </c>
       <c r="B1290" t="s">
-        <v>1475</v>
+        <v>1127</v>
       </c>
       <c r="C1290" t="s">
         <v>14</v>
       </c>
       <c r="D1290" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E1290" t="s">
-        <v>1553</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="1291" spans="1:5" x14ac:dyDescent="0.35">
@@ -27106,16 +27119,16 @@
         <v>716</v>
       </c>
       <c r="B1291" t="s">
-        <v>1475</v>
+        <v>1127</v>
       </c>
       <c r="C1291" t="s">
         <v>14</v>
       </c>
       <c r="D1291" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E1291" t="s">
-        <v>1556</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="1292" spans="1:5" x14ac:dyDescent="0.35">
@@ -27123,50 +27136,50 @@
         <v>716</v>
       </c>
       <c r="B1292" t="s">
-        <v>1475</v>
+        <v>1127</v>
       </c>
       <c r="C1292" t="s">
         <v>14</v>
       </c>
       <c r="D1292" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E1292" t="s">
-        <v>1559</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="1293" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1293" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B1293" t="s">
-        <v>717</v>
+        <v>498</v>
       </c>
       <c r="C1293" t="s">
         <v>14</v>
       </c>
       <c r="D1293" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="E1293" t="s">
-        <v>939</v>
+        <v>526</v>
       </c>
     </row>
     <row r="1294" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1294" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B1294" t="s">
-        <v>717</v>
+        <v>607</v>
       </c>
       <c r="C1294" t="s">
         <v>14</v>
       </c>
       <c r="D1294" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="E1294" t="s">
-        <v>940</v>
+        <v>635</v>
       </c>
     </row>
     <row r="1295" spans="1:5" x14ac:dyDescent="0.35">
@@ -27174,16 +27187,16 @@
         <v>716</v>
       </c>
       <c r="B1295" t="s">
-        <v>717</v>
+        <v>1243</v>
       </c>
       <c r="C1295" t="s">
         <v>14</v>
       </c>
       <c r="D1295" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="E1295" t="s">
-        <v>947</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="1296" spans="1:5" x14ac:dyDescent="0.35">
@@ -27191,16 +27204,16 @@
         <v>716</v>
       </c>
       <c r="B1296" t="s">
-        <v>717</v>
+        <v>1243</v>
       </c>
       <c r="C1296" t="s">
         <v>14</v>
       </c>
       <c r="D1296" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="E1296" t="s">
-        <v>948</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="1297" spans="1:5" x14ac:dyDescent="0.35">
@@ -27208,16 +27221,16 @@
         <v>716</v>
       </c>
       <c r="B1297" t="s">
-        <v>717</v>
+        <v>1243</v>
       </c>
       <c r="C1297" t="s">
         <v>14</v>
       </c>
       <c r="D1297" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="E1297" t="s">
-        <v>949</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="1298" spans="1:5" x14ac:dyDescent="0.35">
@@ -27225,16 +27238,16 @@
         <v>716</v>
       </c>
       <c r="B1298" t="s">
-        <v>1049</v>
+        <v>1243</v>
       </c>
       <c r="C1298" t="s">
         <v>14</v>
       </c>
       <c r="D1298" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="E1298" t="s">
-        <v>1101</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="1299" spans="1:5" x14ac:dyDescent="0.35">
@@ -27242,16 +27255,16 @@
         <v>716</v>
       </c>
       <c r="B1299" t="s">
-        <v>1049</v>
+        <v>1243</v>
       </c>
       <c r="C1299" t="s">
         <v>14</v>
       </c>
       <c r="D1299" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="E1299" t="s">
-        <v>1102</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="1300" spans="1:5" x14ac:dyDescent="0.35">
@@ -27259,16 +27272,16 @@
         <v>716</v>
       </c>
       <c r="B1300" t="s">
-        <v>1127</v>
+        <v>1243</v>
       </c>
       <c r="C1300" t="s">
         <v>14</v>
       </c>
       <c r="D1300" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E1300" t="s">
-        <v>1205</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="1301" spans="1:5" x14ac:dyDescent="0.35">
@@ -27276,16 +27289,16 @@
         <v>716</v>
       </c>
       <c r="B1301" t="s">
-        <v>1127</v>
+        <v>1243</v>
       </c>
       <c r="C1301" t="s">
         <v>14</v>
       </c>
       <c r="D1301" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E1301" t="s">
-        <v>1206</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="1302" spans="1:5" x14ac:dyDescent="0.35">
@@ -27299,10 +27312,10 @@
         <v>14</v>
       </c>
       <c r="D1302" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E1302" t="s">
-        <v>1321</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="1303" spans="1:5" x14ac:dyDescent="0.35">
@@ -27316,10 +27329,10 @@
         <v>14</v>
       </c>
       <c r="D1303" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E1303" t="s">
-        <v>1322</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="1304" spans="1:5" x14ac:dyDescent="0.35">
@@ -27327,16 +27340,16 @@
         <v>716</v>
       </c>
       <c r="B1304" t="s">
-        <v>1359</v>
+        <v>1243</v>
       </c>
       <c r="C1304" t="s">
         <v>14</v>
       </c>
       <c r="D1304" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E1304" t="s">
-        <v>1437</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="1305" spans="1:5" x14ac:dyDescent="0.35">
@@ -27344,16 +27357,16 @@
         <v>716</v>
       </c>
       <c r="B1305" t="s">
-        <v>1359</v>
+        <v>1243</v>
       </c>
       <c r="C1305" t="s">
         <v>14</v>
       </c>
       <c r="D1305" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E1305" t="s">
-        <v>1438</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="1306" spans="1:5" x14ac:dyDescent="0.35">
@@ -27361,16 +27374,16 @@
         <v>716</v>
       </c>
       <c r="B1306" t="s">
-        <v>1475</v>
+        <v>1243</v>
       </c>
       <c r="C1306" t="s">
         <v>14</v>
       </c>
       <c r="D1306" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E1306" t="s">
-        <v>1554</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="1307" spans="1:5" x14ac:dyDescent="0.35">
@@ -27378,16 +27391,16 @@
         <v>716</v>
       </c>
       <c r="B1307" t="s">
-        <v>1475</v>
+        <v>1243</v>
       </c>
       <c r="C1307" t="s">
         <v>14</v>
       </c>
       <c r="D1307" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E1307" t="s">
-        <v>1555</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="1308" spans="1:5" x14ac:dyDescent="0.35">
@@ -27395,16 +27408,16 @@
         <v>716</v>
       </c>
       <c r="B1308" t="s">
-        <v>717</v>
+        <v>1243</v>
       </c>
       <c r="C1308" t="s">
         <v>14</v>
       </c>
       <c r="D1308" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E1308" t="s">
-        <v>942</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="1309" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
@@ -28891,16 +28904,16 @@
         <v>716</v>
       </c>
       <c r="B1396" t="s">
-        <v>717</v>
+        <v>1243</v>
       </c>
       <c r="C1396" t="s">
         <v>14</v>
       </c>
       <c r="D1396" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E1396" t="s">
-        <v>945</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="1397" spans="1:5" x14ac:dyDescent="0.35">
@@ -28908,16 +28921,16 @@
         <v>716</v>
       </c>
       <c r="B1397" t="s">
-        <v>1049</v>
+        <v>1243</v>
       </c>
       <c r="C1397" t="s">
         <v>14</v>
       </c>
       <c r="D1397" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E1397" t="s">
-        <v>1103</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="1398" spans="1:5" x14ac:dyDescent="0.35">
@@ -28925,16 +28938,16 @@
         <v>716</v>
       </c>
       <c r="B1398" t="s">
-        <v>1127</v>
+        <v>1243</v>
       </c>
       <c r="C1398" t="s">
         <v>14</v>
       </c>
       <c r="D1398" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E1398" t="s">
-        <v>1208</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="1399" spans="1:5" x14ac:dyDescent="0.35">
@@ -28942,33 +28955,33 @@
         <v>716</v>
       </c>
       <c r="B1399" t="s">
-        <v>1127</v>
+        <v>1243</v>
       </c>
       <c r="C1399" t="s">
         <v>14</v>
       </c>
       <c r="D1399" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E1399" t="s">
-        <v>1211</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="1400" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1400" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B1400" t="s">
-        <v>1243</v>
+        <v>369</v>
       </c>
       <c r="C1400" t="s">
         <v>14</v>
       </c>
       <c r="D1400" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="E1400" t="s">
-        <v>1324</v>
+        <v>397</v>
       </c>
     </row>
     <row r="1401" spans="1:5" x14ac:dyDescent="0.35">
@@ -28976,16 +28989,16 @@
         <v>716</v>
       </c>
       <c r="B1401" t="s">
-        <v>1243</v>
+        <v>1359</v>
       </c>
       <c r="C1401" t="s">
         <v>14</v>
       </c>
       <c r="D1401" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="E1401" t="s">
-        <v>1327</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="1402" spans="1:5" x14ac:dyDescent="0.35">
@@ -28999,10 +29012,10 @@
         <v>14</v>
       </c>
       <c r="D1402" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="E1402" t="s">
-        <v>1440</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="1403" spans="1:5" x14ac:dyDescent="0.35">
@@ -29016,10 +29029,10 @@
         <v>14</v>
       </c>
       <c r="D1403" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="E1403" t="s">
-        <v>1443</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="1404" spans="1:5" x14ac:dyDescent="0.35">
@@ -29027,16 +29040,16 @@
         <v>716</v>
       </c>
       <c r="B1404" t="s">
-        <v>1475</v>
+        <v>1359</v>
       </c>
       <c r="C1404" t="s">
         <v>14</v>
       </c>
       <c r="D1404" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="E1404" t="s">
-        <v>1557</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="1405" spans="1:5" x14ac:dyDescent="0.35">
@@ -29044,16 +29057,16 @@
         <v>716</v>
       </c>
       <c r="B1405" t="s">
-        <v>1475</v>
+        <v>1359</v>
       </c>
       <c r="C1405" t="s">
         <v>14</v>
       </c>
       <c r="D1405" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="E1405" t="s">
-        <v>1560</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="1406" spans="1:5" x14ac:dyDescent="0.35">
@@ -29061,16 +29074,16 @@
         <v>716</v>
       </c>
       <c r="B1406" t="s">
-        <v>717</v>
+        <v>1359</v>
       </c>
       <c r="C1406" t="s">
         <v>14</v>
       </c>
       <c r="D1406" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E1406" t="s">
-        <v>943</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="1407" spans="1:5" x14ac:dyDescent="0.35">
@@ -29078,16 +29091,16 @@
         <v>716</v>
       </c>
       <c r="B1407" t="s">
-        <v>717</v>
+        <v>1359</v>
       </c>
       <c r="C1407" t="s">
         <v>14</v>
       </c>
       <c r="D1407" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E1407" t="s">
-        <v>946</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="1408" spans="1:5" x14ac:dyDescent="0.35">
@@ -29095,16 +29108,16 @@
         <v>716</v>
       </c>
       <c r="B1408" t="s">
-        <v>1049</v>
+        <v>1359</v>
       </c>
       <c r="C1408" t="s">
         <v>14</v>
       </c>
       <c r="D1408" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E1408" t="s">
-        <v>1104</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="1409" spans="1:5" x14ac:dyDescent="0.35">
@@ -29112,16 +29125,16 @@
         <v>716</v>
       </c>
       <c r="B1409" t="s">
-        <v>1127</v>
+        <v>1359</v>
       </c>
       <c r="C1409" t="s">
         <v>14</v>
       </c>
       <c r="D1409" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E1409" t="s">
-        <v>1209</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1410" spans="1:5" x14ac:dyDescent="0.35">
@@ -29129,16 +29142,16 @@
         <v>716</v>
       </c>
       <c r="B1410" t="s">
-        <v>1127</v>
+        <v>1359</v>
       </c>
       <c r="C1410" t="s">
         <v>14</v>
       </c>
       <c r="D1410" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E1410" t="s">
-        <v>1212</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="1411" spans="1:5" x14ac:dyDescent="0.35">
@@ -29146,33 +29159,33 @@
         <v>716</v>
       </c>
       <c r="B1411" t="s">
-        <v>1243</v>
+        <v>1359</v>
       </c>
       <c r="C1411" t="s">
         <v>14</v>
       </c>
       <c r="D1411" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="E1411" t="s">
-        <v>1325</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="1412" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1412" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B1412" t="s">
-        <v>1243</v>
+        <v>275</v>
       </c>
       <c r="C1412" t="s">
         <v>14</v>
       </c>
       <c r="D1412" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="E1412" t="s">
-        <v>1328</v>
+        <v>300</v>
       </c>
     </row>
     <row r="1413" spans="1:5" x14ac:dyDescent="0.35">
@@ -29186,10 +29199,10 @@
         <v>14</v>
       </c>
       <c r="D1413" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E1413" t="s">
-        <v>1441</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="1414" spans="1:5" x14ac:dyDescent="0.35">
@@ -29203,10 +29216,10 @@
         <v>14</v>
       </c>
       <c r="D1414" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E1414" t="s">
-        <v>1444</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="1415" spans="1:5" x14ac:dyDescent="0.35">
@@ -29214,16 +29227,16 @@
         <v>716</v>
       </c>
       <c r="B1415" t="s">
-        <v>1475</v>
+        <v>1359</v>
       </c>
       <c r="C1415" t="s">
         <v>14</v>
       </c>
       <c r="D1415" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E1415" t="s">
-        <v>1558</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1416" spans="1:5" x14ac:dyDescent="0.35">
@@ -29231,16 +29244,16 @@
         <v>716</v>
       </c>
       <c r="B1416" t="s">
-        <v>1475</v>
+        <v>1359</v>
       </c>
       <c r="C1416" t="s">
         <v>14</v>
       </c>
       <c r="D1416" t="s">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="E1416" t="s">
-        <v>1561</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="1417" spans="1:5" x14ac:dyDescent="0.35">
@@ -29248,16 +29261,16 @@
         <v>716</v>
       </c>
       <c r="B1417" t="s">
-        <v>717</v>
+        <v>1359</v>
       </c>
       <c r="C1417" t="s">
         <v>14</v>
       </c>
       <c r="D1417" t="s">
-        <v>794</v>
+        <v>48</v>
       </c>
       <c r="E1417" t="s">
-        <v>958</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="1418" spans="1:5" x14ac:dyDescent="0.35">
@@ -29265,16 +29278,16 @@
         <v>716</v>
       </c>
       <c r="B1418" t="s">
-        <v>717</v>
+        <v>1359</v>
       </c>
       <c r="C1418" t="s">
         <v>14</v>
       </c>
       <c r="D1418" t="s">
-        <v>794</v>
+        <v>48</v>
       </c>
       <c r="E1418" t="s">
-        <v>950</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="1419" spans="1:5" x14ac:dyDescent="0.35">
@@ -29282,33 +29295,33 @@
         <v>716</v>
       </c>
       <c r="B1419" t="s">
-        <v>717</v>
+        <v>1359</v>
       </c>
       <c r="C1419" t="s">
         <v>14</v>
       </c>
       <c r="D1419" t="s">
-        <v>794</v>
+        <v>48</v>
       </c>
       <c r="E1419" t="s">
-        <v>959</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="1420" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1420" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B1420" t="s">
-        <v>717</v>
+        <v>6</v>
       </c>
       <c r="C1420" t="s">
         <v>14</v>
       </c>
       <c r="D1420" t="s">
-        <v>794</v>
+        <v>8</v>
       </c>
       <c r="E1420" t="s">
-        <v>960</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1421" spans="1:5" x14ac:dyDescent="0.35">
@@ -29316,16 +29329,16 @@
         <v>716</v>
       </c>
       <c r="B1421" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C1421" t="s">
         <v>14</v>
       </c>
       <c r="D1421" t="s">
-        <v>794</v>
+        <v>8</v>
       </c>
       <c r="E1421" t="s">
-        <v>961</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="1422" spans="1:5" x14ac:dyDescent="0.35">
@@ -29333,16 +29346,16 @@
         <v>716</v>
       </c>
       <c r="B1422" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C1422" t="s">
         <v>14</v>
       </c>
       <c r="D1422" t="s">
-        <v>794</v>
+        <v>8</v>
       </c>
       <c r="E1422" t="s">
-        <v>962</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="1423" spans="1:5" x14ac:dyDescent="0.35">
@@ -29350,16 +29363,16 @@
         <v>716</v>
       </c>
       <c r="B1423" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C1423" t="s">
         <v>14</v>
       </c>
       <c r="D1423" t="s">
-        <v>794</v>
+        <v>8</v>
       </c>
       <c r="E1423" t="s">
-        <v>963</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="1424" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
@@ -30863,16 +30876,16 @@
         <v>716</v>
       </c>
       <c r="B1512" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C1512" t="s">
         <v>14</v>
       </c>
       <c r="D1512" t="s">
-        <v>794</v>
+        <v>8</v>
       </c>
       <c r="E1512" t="s">
-        <v>964</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="1513" spans="1:5" x14ac:dyDescent="0.35">
@@ -30880,16 +30893,16 @@
         <v>716</v>
       </c>
       <c r="B1513" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C1513" t="s">
         <v>14</v>
       </c>
       <c r="D1513" t="s">
-        <v>794</v>
+        <v>8</v>
       </c>
       <c r="E1513" t="s">
-        <v>965</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="1514" spans="1:5" x14ac:dyDescent="0.35">
@@ -30897,16 +30910,16 @@
         <v>716</v>
       </c>
       <c r="B1514" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C1514" t="s">
         <v>14</v>
       </c>
       <c r="D1514" t="s">
-        <v>794</v>
+        <v>45</v>
       </c>
       <c r="E1514" t="s">
-        <v>966</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="1515" spans="1:5" x14ac:dyDescent="0.35">
@@ -30914,16 +30927,16 @@
         <v>716</v>
       </c>
       <c r="B1515" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C1515" t="s">
         <v>14</v>
       </c>
       <c r="D1515" t="s">
-        <v>794</v>
+        <v>45</v>
       </c>
       <c r="E1515" t="s">
-        <v>967</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="1516" spans="1:5" x14ac:dyDescent="0.35">
@@ -30931,16 +30944,16 @@
         <v>716</v>
       </c>
       <c r="B1516" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C1516" t="s">
         <v>14</v>
       </c>
       <c r="D1516" t="s">
-        <v>794</v>
+        <v>45</v>
       </c>
       <c r="E1516" t="s">
-        <v>968</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="1517" spans="1:5" x14ac:dyDescent="0.35">
@@ -30948,16 +30961,16 @@
         <v>716</v>
       </c>
       <c r="B1517" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C1517" t="s">
         <v>14</v>
       </c>
       <c r="D1517" t="s">
-        <v>794</v>
+        <v>45</v>
       </c>
       <c r="E1517" t="s">
-        <v>951</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="1518" spans="1:5" x14ac:dyDescent="0.35">
@@ -30965,16 +30978,16 @@
         <v>716</v>
       </c>
       <c r="B1518" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C1518" t="s">
         <v>14</v>
       </c>
       <c r="D1518" t="s">
-        <v>794</v>
+        <v>45</v>
       </c>
       <c r="E1518" t="s">
-        <v>952</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="1519" spans="1:5" x14ac:dyDescent="0.35">
@@ -30982,16 +30995,16 @@
         <v>716</v>
       </c>
       <c r="B1519" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C1519" t="s">
         <v>14</v>
       </c>
       <c r="D1519" t="s">
-        <v>794</v>
+        <v>45</v>
       </c>
       <c r="E1519" t="s">
-        <v>953</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="1520" spans="1:5" x14ac:dyDescent="0.35">
@@ -30999,16 +31012,16 @@
         <v>716</v>
       </c>
       <c r="B1520" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C1520" t="s">
         <v>14</v>
       </c>
       <c r="D1520" t="s">
-        <v>794</v>
+        <v>48</v>
       </c>
       <c r="E1520" t="s">
-        <v>954</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="1521" spans="1:5" x14ac:dyDescent="0.35">
@@ -31016,16 +31029,16 @@
         <v>716</v>
       </c>
       <c r="B1521" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C1521" t="s">
         <v>14</v>
       </c>
       <c r="D1521" t="s">
-        <v>794</v>
+        <v>48</v>
       </c>
       <c r="E1521" t="s">
-        <v>969</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="1522" spans="1:5" x14ac:dyDescent="0.35">
@@ -31033,16 +31046,16 @@
         <v>716</v>
       </c>
       <c r="B1522" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C1522" t="s">
         <v>14</v>
       </c>
       <c r="D1522" t="s">
-        <v>794</v>
+        <v>48</v>
       </c>
       <c r="E1522" t="s">
-        <v>970</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="1523" spans="1:5" x14ac:dyDescent="0.35">
@@ -31050,16 +31063,16 @@
         <v>716</v>
       </c>
       <c r="B1523" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C1523" t="s">
         <v>14</v>
       </c>
       <c r="D1523" t="s">
-        <v>794</v>
+        <v>48</v>
       </c>
       <c r="E1523" t="s">
-        <v>971</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="1524" spans="1:5" x14ac:dyDescent="0.35">
@@ -31067,16 +31080,16 @@
         <v>716</v>
       </c>
       <c r="B1524" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C1524" t="s">
         <v>14</v>
       </c>
       <c r="D1524" t="s">
-        <v>794</v>
+        <v>48</v>
       </c>
       <c r="E1524" t="s">
-        <v>972</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="1525" spans="1:5" x14ac:dyDescent="0.35">
@@ -31084,16 +31097,16 @@
         <v>716</v>
       </c>
       <c r="B1525" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C1525" t="s">
         <v>14</v>
       </c>
       <c r="D1525" t="s">
-        <v>794</v>
+        <v>48</v>
       </c>
       <c r="E1525" t="s">
-        <v>955</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="1526" spans="1:5" x14ac:dyDescent="0.35">
@@ -31101,237 +31114,237 @@
         <v>716</v>
       </c>
       <c r="B1526" t="s">
-        <v>717</v>
+        <v>1475</v>
       </c>
       <c r="C1526" t="s">
         <v>14</v>
       </c>
       <c r="D1526" t="s">
-        <v>794</v>
+        <v>48</v>
       </c>
       <c r="E1526" t="s">
-        <v>956</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="1527" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1527" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B1527" t="s">
-        <v>717</v>
+        <v>146</v>
       </c>
       <c r="C1527" t="s">
         <v>14</v>
       </c>
       <c r="D1527" t="s">
-        <v>794</v>
+        <v>8</v>
       </c>
       <c r="E1527" t="s">
-        <v>957</v>
+        <v>174</v>
       </c>
     </row>
     <row r="1528" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1528" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B1528" t="s">
-        <v>717</v>
+        <v>498</v>
       </c>
       <c r="C1528" t="s">
         <v>14</v>
       </c>
       <c r="D1528" t="s">
-        <v>802</v>
+        <v>8</v>
       </c>
       <c r="E1528" t="s">
-        <v>973</v>
+        <v>524</v>
       </c>
     </row>
     <row r="1529" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1529" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B1529" t="s">
-        <v>717</v>
+        <v>607</v>
       </c>
       <c r="C1529" t="s">
         <v>14</v>
       </c>
       <c r="D1529" t="s">
-        <v>802</v>
+        <v>8</v>
       </c>
       <c r="E1529" t="s">
-        <v>974</v>
+        <v>633</v>
       </c>
     </row>
     <row r="1530" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1530" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B1530" t="s">
-        <v>717</v>
+        <v>369</v>
       </c>
       <c r="C1530" t="s">
         <v>14</v>
       </c>
       <c r="D1530" t="s">
-        <v>802</v>
+        <v>8</v>
       </c>
       <c r="E1530" t="s">
-        <v>975</v>
+        <v>395</v>
       </c>
     </row>
     <row r="1531" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1531" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B1531" t="s">
-        <v>717</v>
+        <v>275</v>
       </c>
       <c r="C1531" t="s">
         <v>14</v>
       </c>
       <c r="D1531" t="s">
-        <v>802</v>
+        <v>8</v>
       </c>
       <c r="E1531" t="s">
-        <v>976</v>
+        <v>298</v>
       </c>
     </row>
     <row r="1532" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1532" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B1532" t="s">
-        <v>717</v>
+        <v>6</v>
       </c>
       <c r="C1532" t="s">
         <v>14</v>
       </c>
       <c r="D1532" t="s">
-        <v>802</v>
+        <v>8</v>
       </c>
       <c r="E1532" t="s">
-        <v>977</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1533" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1533" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B1533" t="s">
-        <v>717</v>
+        <v>146</v>
       </c>
       <c r="C1533" t="s">
         <v>14</v>
       </c>
       <c r="D1533" t="s">
-        <v>802</v>
+        <v>8</v>
       </c>
       <c r="E1533" t="s">
-        <v>978</v>
+        <v>172</v>
       </c>
     </row>
     <row r="1534" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1534" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B1534" t="s">
-        <v>717</v>
+        <v>498</v>
       </c>
       <c r="C1534" t="s">
         <v>14</v>
       </c>
       <c r="D1534" t="s">
-        <v>802</v>
+        <v>8</v>
       </c>
       <c r="E1534" t="s">
-        <v>979</v>
+        <v>525</v>
       </c>
     </row>
     <row r="1535" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1535" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B1535" t="s">
-        <v>717</v>
+        <v>607</v>
       </c>
       <c r="C1535" t="s">
         <v>14</v>
       </c>
       <c r="D1535" t="s">
-        <v>802</v>
+        <v>8</v>
       </c>
       <c r="E1535" t="s">
-        <v>980</v>
+        <v>634</v>
       </c>
     </row>
     <row r="1536" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1536" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B1536" t="s">
-        <v>717</v>
+        <v>369</v>
       </c>
       <c r="C1536" t="s">
         <v>14</v>
       </c>
       <c r="D1536" t="s">
-        <v>802</v>
+        <v>8</v>
       </c>
       <c r="E1536" t="s">
-        <v>981</v>
+        <v>396</v>
       </c>
     </row>
     <row r="1537" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1537" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B1537" t="s">
-        <v>717</v>
+        <v>275</v>
       </c>
       <c r="C1537" t="s">
         <v>14</v>
       </c>
       <c r="D1537" t="s">
-        <v>802</v>
+        <v>8</v>
       </c>
       <c r="E1537" t="s">
-        <v>982</v>
+        <v>299</v>
       </c>
     </row>
     <row r="1538" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1538" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B1538" t="s">
-        <v>717</v>
+        <v>6</v>
       </c>
       <c r="C1538" t="s">
         <v>14</v>
       </c>
       <c r="D1538" t="s">
-        <v>844</v>
+        <v>8</v>
       </c>
       <c r="E1538" t="s">
-        <v>983</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1539" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1539" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
       <c r="B1539" t="s">
-        <v>717</v>
+        <v>146</v>
       </c>
       <c r="C1539" t="s">
         <v>14</v>
       </c>
       <c r="D1539" t="s">
-        <v>844</v>
+        <v>8</v>
       </c>
       <c r="E1539" t="s">
-        <v>984</v>
+        <v>173</v>
       </c>
     </row>
     <row r="1540" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
@@ -31852,7 +31865,7 @@
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:E1539">
-      <sortCondition ref="D1:D1569"/>
+      <sortCondition ref="E1:E1569"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
